--- a/AI_AuditLog_Example_HoangNhatKha.xlsx
+++ b/AI_AuditLog_Example_HoangNhatKha.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_UNIVERSITY\Kì 5\5.SWP391\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_UNIVERSITY\Kì 5\5.SWP391\swp391-aiauditlog-nhatkhaiphone-ux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE0A72FC-B1DF-4AC8-8670-B3410A4BEFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87411A24-CA6C-490A-BD99-9E08933A8A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="242">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -628,6 +628,141 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>The SRS needs clearer Introduction, Scope, and Existing Systems sections for the RentalRoom topic.</t>
+  </si>
+  <si>
+    <t>Create Introduction, Scope, and Existing Systems for a RentalRoom search and booking system. Keep it formal for SRS.</t>
+  </si>
+  <si>
+    <t>AI suggested describing RentalRoom as a platform for tenants, landlords, and admin, including searching rooms, posting rooms, booking, deposit, chat, notification, and management.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI provided a good structure but the first version was too general and used broad accommodation examples. Contextualization: Our project is specifically RentalRoom, not hotel booking. Creative Synthesis: I rewrote the content to focus on long-term room rental for students and workers. Decision Ownership: I chose to add these sections before Product Overview to make the SRS more complete and easier to present.</t>
+  </si>
+  <si>
+    <t>Updated SRS Introduction/Scope/Existing Systems section</t>
+  </si>
+  <si>
+    <t>The ERD relationships need to be explained clearly when the teacher asks about one-to-many or many-to-many relations.</t>
+  </si>
+  <si>
+    <t>Explain RentalRoom database relationships such as User-Profile, Room-Booking, Room-Contract, Contract-Payment, and Contract-Occupant in simple terms.</t>
+  </si>
+  <si>
+    <t>AI explained common relationships: one user has one profile, one landlord has many rooms, one room has many booking requests, one rental contract can include multiple occupants, and payments belong to rental contracts.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: The explanation was useful but some relationships needed adjustment to match the actual ERD. Contextualization: In our design, payment and contract logic must follow the deposit/rental flow. Creative Synthesis: I prepared a simplified explanation using examples that can be spoken in presentation. Decision Ownership: I kept only relationships that exist in our database to avoid explaining fake tables.</t>
+  </si>
+  <si>
+    <t>ERD relationship explanation notes</t>
+  </si>
+  <si>
+    <t>The use case diagram may become too complicated if every feature includes Login or Notification.</t>
+  </si>
+  <si>
+    <t>Check whether Login and Send Notification should be included or extended in every RentalRoom use case diagram.</t>
+  </si>
+  <si>
+    <t>AI explained that Login is normally a precondition for protected features, while Notification can be modeled as an included or supporting function only for flows that actually trigger messages.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI was correct, but it may confuse the diagram if overused. Contextualization: The teacher prefers a clean and logical use case diagram. Creative Synthesis: I separated Authentication and used preconditions for login-required functions; notifications are connected only to important events such as booking approval, payment, and cancellation. Decision Ownership: I chose clarity over showing every technical dependency.</t>
+  </si>
+  <si>
+    <t>Use case diagram revision + presentation explanation</t>
+  </si>
+  <si>
+    <t>The room booking process needs a clear status lifecycle from request to deposit to rental contract.</t>
+  </si>
+  <si>
+    <t>Design a status flow for rental request and room reservation in RentalRoom after tenant views a room and wants to rent it.</t>
+  </si>
+  <si>
+    <t>AI suggested statuses such as Pending, Approved, Pending Payment, Deposited, Contract Created, Rejected, Cancelled, and Expired.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI's status list is helpful but needs rules for who can change each status. Contextualization: Landlord approves the request first, then tenant pays deposit before the contract is created. Creative Synthesis: I created a lifecycle: Request Submitted → Approved → Pending Deposit → Deposited → Contract Created; failure paths include Rejected, Cancelled, and Expired. Decision Ownership: This flow was selected because it matches the team's business rule: view room, deposit, then rent room.</t>
+  </si>
+  <si>
+    <t>State diagram / booking flow update</t>
+  </si>
+  <si>
+    <t>The team needs weekly Jira update content showing what was completed for the SRS and AI audit log.</t>
+  </si>
+  <si>
+    <t>Write a short Jira week update for completing RentalRoom SRS Introduction, Scope, Existing Systems, and AI Audit Log entries.</t>
+  </si>
+  <si>
+    <t>AI suggested a concise update: completed SRS sections, updated audit log entries, reviewed hallucination cases, and prepared evidence for presentation.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI output was acceptable but too generic. Contextualization: The update must match the actual tasks completed this week. Creative Synthesis: I customized the update to mention RentalRoom SRS, database/use case explanation, booking status flow, and audit log update. Decision Ownership: I used this wording so the Jira record is specific and traceable.</t>
+  </si>
+  <si>
+    <t>Jira Week 2 update/comment</t>
+  </si>
+  <si>
+    <t>Existing systems for RentalRoom can be described mainly using hotel booking platforms.</t>
+  </si>
+  <si>
+    <t>Rental request only needs Approved and Rejected statuses.</t>
+  </si>
+  <si>
+    <t>Hotel booking platforms are related but not fully the same as long-term room rental systems for students/workers.</t>
+  </si>
+  <si>
+    <t>The booking flow also needs Pending Deposit, Deposited, Cancelled, and Expired to handle real business cases.</t>
+  </si>
+  <si>
+    <t>Compared the topic name and scope with RentalRoom business requirements.</t>
+  </si>
+  <si>
+    <t>Checked the flow from viewing room → landlord approval → deposit → rental contract.</t>
+  </si>
+  <si>
+    <t>Rewrote Existing Systems to include Facebook Marketplace, Chợ Tốt, Phongtro123, Airbnb/Booking only as comparable references.</t>
+  </si>
+  <si>
+    <t>Added a clearer status lifecycle for rental request and payment deadline.</t>
+  </si>
+  <si>
+    <t>Có – chọn filter truyền thống làm core vì dễ test và đúng yêu cầu tìm phòng</t>
+  </si>
+  <si>
+    <t>Có – thêm RentalContract/Occupant để quản lý lịch sử thuê và nhiều người ở chung</t>
+  </si>
+  <si>
+    <t>Có – phát hiện currentTenantId trong Room không đủ cho lịch sử thuê</t>
+  </si>
+  <si>
+    <t>Có – thêm deadline thanh toán để tránh landlord phải chờ quá lâu</t>
+  </si>
+  <si>
+    <t>Có – Login nên là precondition để use case diagram gọn hơn</t>
+  </si>
+  <si>
+    <t>Có – Scope/Existing Systems giúp SRS đúng chủ đề RentalRoom</t>
+  </si>
+  <si>
+    <t>Có – thêm transactionId để tránh lỗi payment trùng hoặc sai trạng thái</t>
+  </si>
+  <si>
+    <t>Có – Introduction/Scope cần tập trung vào thuê phòng dài hạn</t>
+  </si>
+  <si>
+    <t>Có – giải thích quan hệ ERD bằng ví dụ để dễ trình bày với giáo viên</t>
+  </si>
+  <si>
+    <t>Có – tách Authentication và Notification để diagram không bị rối</t>
+  </si>
+  <si>
+    <t>Có – status lifecycle giúp booking flow rõ từ request đến contract</t>
+  </si>
+  <si>
+    <t>Có – Jira update cần cụ thể task đã làm trong tuần 2</t>
   </si>
 </sst>
 </file>
@@ -802,7 +937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -837,22 +972,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -876,6 +995,25 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1190,14 +1328,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1245,24 +1383,24 @@
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="22">
-        <v>60</v>
+      <c r="C10" s="16">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="23">
-        <v>10</v>
+      <c r="C11" s="17">
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="24">
-        <v>0.16669999999999999</v>
+      <c r="C12" s="18">
+        <v>0.2</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>10</v>
@@ -1272,8 +1410,8 @@
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="23">
-        <v>3</v>
+      <c r="C13" s="17">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1299,7 +1437,7 @@
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="19" t="s">
         <v>106</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -1310,30 +1448,30 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="19" t="s">
         <v>108</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="19" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="19" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1341,27 +1479,27 @@
       <c r="A20" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="19" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="16" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1397,7 +1535,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>26</v>
@@ -1419,7 +1557,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>26</v>
@@ -1448,28 +1586,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
@@ -1507,19 +1645,19 @@
       <c r="C4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="19" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1527,25 +1665,25 @@
       <c r="A5" s="5">
         <v>2</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="19" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1553,25 +1691,25 @@
       <c r="A6" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="19" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1579,25 +1717,25 @@
       <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="19" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1605,25 +1743,25 @@
       <c r="A8" s="5">
         <v>5</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="19" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1631,25 +1769,25 @@
       <c r="A9" s="5">
         <v>6</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="19" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1657,25 +1795,25 @@
       <c r="A10" s="5">
         <v>7</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="19" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1683,25 +1821,25 @@
       <c r="A11" s="5">
         <v>8</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="19" t="s">
         <v>143</v>
       </c>
     </row>
@@ -1709,25 +1847,25 @@
       <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="19" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1735,77 +1873,157 @@
       <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="19" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+    <row r="14" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="19">
+        <v>11</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>12</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
+        <v>13</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>14</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
+        <v>15</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
@@ -1907,24 +2125,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
@@ -1950,19 +2168,19 @@
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="19" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1970,19 +2188,19 @@
       <c r="A5" s="5">
         <v>6</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="19" t="s">
         <v>176</v>
       </c>
     </row>
@@ -1990,37 +2208,61 @@
       <c r="A6" s="5">
         <v>10</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="19" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+    <row r="7" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>11</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>14</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
@@ -2232,7 +2474,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2242,20 +2484,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2283,10 +2525,10 @@
       <c r="B6" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="22" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2297,10 +2539,10 @@
       <c r="B7" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="22" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2311,10 +2553,10 @@
       <c r="B8" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="22" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2325,10 +2567,10 @@
       <c r="B9" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="23" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2339,10 +2581,10 @@
       <c r="B10" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="22" t="s">
         <v>187</v>
       </c>
     </row>
@@ -2372,10 +2614,10 @@
       <c r="B14" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="22" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2386,10 +2628,10 @@
       <c r="B15" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="22" t="s">
         <v>189</v>
       </c>
     </row>
@@ -2400,10 +2642,10 @@
       <c r="B16" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="22" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2414,10 +2656,10 @@
       <c r="B17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="22" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2428,10 +2670,10 @@
       <c r="B18" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="22" t="s">
         <v>192</v>
       </c>
     </row>
@@ -2513,6 +2755,174 @@
         <v>196</v>
       </c>
       <c r="D30" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="30">
+        <v>4</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C31" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="30">
+        <v>5</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="30">
+        <v>6</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" t="s">
+        <v>196</v>
+      </c>
+      <c r="D33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="30">
+        <v>7</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="30">
+        <v>8</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" t="s">
+        <v>196</v>
+      </c>
+      <c r="D35" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="30">
+        <v>9</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="30">
+        <v>10</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C37" t="s">
+        <v>196</v>
+      </c>
+      <c r="D37" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="30">
+        <v>11</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" t="s">
+        <v>196</v>
+      </c>
+      <c r="D38" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="30">
+        <v>12</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C39" t="s">
+        <v>196</v>
+      </c>
+      <c r="D39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="30">
+        <v>13</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="30">
+        <v>14</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C41" t="s">
+        <v>196</v>
+      </c>
+      <c r="D41" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="30">
+        <v>15</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" t="s">
         <v>196</v>
       </c>
     </row>

--- a/AI_AuditLog_Example_HoangNhatKha.xlsx
+++ b/AI_AuditLog_Example_HoangNhatKha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_UNIVERSITY\Kì 5\5.SWP391\swp391-aiauditlog-nhatkhaiphone-ux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87411A24-CA6C-490A-BD99-9E08933A8A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BBBB51-C21D-44FF-8BE5-9EDB05E1625C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="314">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -763,6 +763,222 @@
   </si>
   <si>
     <t>Có – Jira update cần cụ thể task đã làm trong tuần 2</t>
+  </si>
+  <si>
+    <t>Week 3 starts frontend implementation, so the UI must be broken into clear pages and reusable components.</t>
+  </si>
+  <si>
+    <t>Break down the RentalRoom frontend into pages, components, and user flows for Tenant, Landlord, and Admin.</t>
+  </si>
+  <si>
+    <t>AI suggested pages: Home, Room List, Room Detail, Login/Register, Tenant Dashboard, Landlord Room Management, Booking/Request, Profile, and Admin moderation.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI gave a good structure, but I reduced it to screens needed for the current sprint. Contextualization: focus on Tenant search flow and auth screens first. Verification: compared with use case diagram. Decision: create reusable components such as Navbar, RoomCard, FilterBar, AuthForm, and ProfileForm.</t>
+  </si>
+  <si>
+    <t>Frontend sitemap + component folder draft</t>
+  </si>
+  <si>
+    <t>The room search UI needs to support common user behavior: search by location, filter by price, and view room details.</t>
+  </si>
+  <si>
+    <t>Design the frontend flow for searching rental rooms with filters and room cards.</t>
+  </si>
+  <si>
+    <t>AI suggested a search bar, filter panel, room cards with price/location/area, and a detail page with images and contact/request buttons.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: The suggestion fits user behavior, but some fields were too complex for week 3. Contextualization: keep location, price range, room type, and facilities. Verification: matched with RentalRoom search use case. Decision: separate SearchPage, FilterSidebar, RoomList, and RoomCard components.</t>
+  </si>
+  <si>
+    <t>Search page wireframe + component list</t>
+  </si>
+  <si>
+    <t>The UI design needs consistent layout and naming so that the team can code React components without confusion.</t>
+  </si>
+  <si>
+    <t>Suggest a clean React frontend structure and naming convention for a rental room web app.</t>
+  </si>
+  <si>
+    <t>AI suggested organizing src into components, pages, services, hooks, assets, and routes, with PascalCase component names.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI structure is useful but too broad for a small student project. Contextualization: keep components/pages/routes/services only. Verification: checked against current React project structure. Decision: use simple folders to avoid overengineering.</t>
+  </si>
+  <si>
+    <t>React folder structure screenshot</t>
+  </si>
+  <si>
+    <t>The AI suggested only desktop UI, but the system will likely be used on phones by tenants.</t>
+  </si>
+  <si>
+    <t>Check possible issues in a desktop-first RentalRoom frontend design.</t>
+  </si>
+  <si>
+    <t>AI identified risks such as small filter sidebar on mobile, overcrowded room cards, and difficult form input on small screens.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: HALLUCINATION/OVERSIMPLIFICATION DETECTED: the first UI plan ignored responsive behavior. Contextualization: most tenants may search using mobile. Verification: reviewed screen widths in browser dev tools. Decision: make filter collapsible on mobile and room cards stack vertically.</t>
+  </si>
+  <si>
+    <t>Responsive UI checklist</t>
+  </si>
+  <si>
+    <t>The Login/Register/Forgot Password pages need validation rules before connecting to backend.</t>
+  </si>
+  <si>
+    <t>Write frontend validation rules for login, register, forgot password, and update profile forms.</t>
+  </si>
+  <si>
+    <t>AI suggested required email/password, password length, confirm password matching, phone format, and avatar/file validation.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI's rules are mostly correct, but password policy should not be too strict for prototype. Contextualization: apply basic validation first. Verification: tested invalid input cases manually. Decision: show inline error messages and disable submit when required fields are invalid.</t>
+  </si>
+  <si>
+    <t>Auth form validation notes</t>
+  </si>
+  <si>
+    <t>Week 4 starts backend authentication, so the backend auth module must be separated into API endpoints and services.</t>
+  </si>
+  <si>
+    <t>Break down backend authentication features for RentalRoom: register, login, logout, Google login, forgot password, update profile.</t>
+  </si>
+  <si>
+    <t>AI suggested controllers/services/routes for Auth, User/Profile, OTP/Email, Google OAuth, and token handling.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI decomposition is suitable, but Google login and OTP require external services. Contextualization: implement normal auth first, then Google/forgot password. Verification: compared with sprint scope. Decision: separate auth.controller, auth.service, profile.controller, and middleware/authMiddleware.</t>
+  </si>
+  <si>
+    <t>Backend auth module plan</t>
+  </si>
+  <si>
+    <t>The database needs fields and relationships to support authentication and user profile updates.</t>
+  </si>
+  <si>
+    <t>Design database fields for users, profiles, OTP reset, and Google login in RentalRoom.</t>
+  </si>
+  <si>
+    <t>AI suggested Users table with email, passwordHash, role, status, googleId, createdAt; Profiles table with fullName, phone, avatar, address; PasswordResetOtp table.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI output is good but must not store raw password or raw OTP. Contextualization: store passwordHash and hashed OTP/expiry. Verification: checked security requirements. Decision: update schema with passwordHash, provider, googleId, resetOtpHash, resetOtpExpires.</t>
+  </si>
+  <si>
+    <t>Auth database schema update</t>
+  </si>
+  <si>
+    <t>The AI recommended storing JWT in localStorage, but this may create security issues.</t>
+  </si>
+  <si>
+    <t>Verify whether JWT should be stored in localStorage or httpOnly cookie for a rental room web app.</t>
+  </si>
+  <si>
+    <t>AI explained localStorage is easier but vulnerable to XSS, while httpOnly cookies reduce token theft risk.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: HALLUCINATION/OVERSIMPLIFICATION DETECTED: the first recommendation was too simple for authentication security. Contextualization: use httpOnly cookie or safer token handling for backend auth. Verification: discussed XSS risk and logout behavior. Decision: avoid relying only on localStorage for sensitive token storage.</t>
+  </si>
+  <si>
+    <t>Auth security note + token handling decision</t>
+  </si>
+  <si>
+    <t>Forgot password flow must be secure and should not reveal whether an email exists.</t>
+  </si>
+  <si>
+    <t>Write backend flow for forgot password using OTP/email verification.</t>
+  </si>
+  <si>
+    <t>AI suggested request reset → generate OTP → email OTP → verify OTP → set new password → invalidate OTP.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI flow is correct, but the response message should be generic. Contextualization: avoid user enumeration. Verification: checked edge cases: expired OTP, wrong OTP, reused OTP. Decision: return 'If the email exists, an OTP has been sent' and limit OTP attempts.</t>
+  </si>
+  <si>
+    <t>Forgot password API flow</t>
+  </si>
+  <si>
+    <t>Update profile must not allow users to change protected fields such as role or account status.</t>
+  </si>
+  <si>
+    <t>Check security risks when implementing update profile API.</t>
+  </si>
+  <si>
+    <t>AI identified mass assignment risk, missing authentication middleware, and lack of file validation for avatar upload.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI correctly found risks, but implementation must whitelist fields. Contextualization: users can update name, phone, address, avatar only. Verification: reviewed request body fields. Decision: reject role/status changes and require authenticated user for profile update.</t>
+  </si>
+  <si>
+    <t>Update profile validation checklist</t>
+  </si>
+  <si>
+    <t>Desktop UI design is enough for the first frontend sprint.</t>
+  </si>
+  <si>
+    <t>JWT can simply be stored in localStorage for login sessions.</t>
+  </si>
+  <si>
+    <t>Forgot password API can say 'email not found' when the account does not exist.</t>
+  </si>
+  <si>
+    <t>Tenants often search rooms on mobile, so responsive behavior is necessary.</t>
+  </si>
+  <si>
+    <t>localStorage is vulnerable to token theft through XSS; safer handling is needed for authentication.</t>
+  </si>
+  <si>
+    <t>This can reveal registered emails and create user enumeration risk.</t>
+  </si>
+  <si>
+    <t>Reviewed frontend screen in browser dev tools and checked search/filter usability on smaller width.</t>
+  </si>
+  <si>
+    <t>Compared token storage risks and reviewed logout/session behavior.</t>
+  </si>
+  <si>
+    <t>Checked security edge cases for forgot password flow.</t>
+  </si>
+  <si>
+    <t>Added responsive rules: collapsible filter, stacked room cards, and mobile-friendly form spacing.</t>
+  </si>
+  <si>
+    <t>Avoid relying only on localStorage; prefer httpOnly cookie or safer token strategy.</t>
+  </si>
+  <si>
+    <t>Use generic response: 'If the email exists, an OTP has been sent', and limit OTP attempts.</t>
+  </si>
+  <si>
+    <t>Có – tách frontend thành page/component để team dễ chia việc và code React</t>
+  </si>
+  <si>
+    <t>Có – search/filter UI bám sát hành vi tenant tìm phòng</t>
+  </si>
+  <si>
+    <t>Có – folder structure đơn giản giúp tránh overengineering</t>
+  </si>
+  <si>
+    <t>Có – phát hiện UI desktop-first thiếu responsive mobile</t>
+  </si>
+  <si>
+    <t>Có – validation frontend giúp giảm lỗi trước khi gọi API</t>
+  </si>
+  <si>
+    <t>Có – tách auth backend thành controller/service/middleware rõ ràng</t>
+  </si>
+  <si>
+    <t>Có – schema auth cần passwordHash, Google ID và OTP reset an toàn</t>
+  </si>
+  <si>
+    <t>Có – token storage cần cân nhắc bảo mật thay vì chỉ localStorage</t>
+  </si>
+  <si>
+    <t>Có – forgot password phải tránh lộ email tồn tại trong hệ thống</t>
+  </si>
+  <si>
+    <t>Có – update profile phải whitelist field để tránh đổi role/status</t>
   </si>
 </sst>
 </file>
@@ -937,7 +1153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -996,6 +1212,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1012,8 +1231,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1328,14 +1553,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1384,7 +1609,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="16">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1392,7 +1617,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="17">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1400,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="18">
-        <v>0.2</v>
+        <v>0.17860000000000001</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>10</v>
@@ -1411,7 +1636,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="17">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1524,7 +1749,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>26</v>
@@ -1535,7 +1760,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>26</v>
@@ -1546,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>26</v>
@@ -1557,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>26</v>
@@ -1573,7 +1798,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1586,28 +1811,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
@@ -2025,85 +2250,265 @@
         <v>221</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+    <row r="19" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="19">
+        <v>16</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="19">
+        <v>17</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="19">
+        <v>18</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="19">
+        <v>19</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="19">
+        <v>20</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="19">
+        <v>21</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="19">
+        <v>22</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="123.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="19">
+        <v>23</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="31">
+        <v>24</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="31">
+        <v>25</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="H28" s="31" t="s">
+        <v>291</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2125,24 +2530,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
@@ -2264,29 +2669,65 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+    <row r="9" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="19">
+        <v>19</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="19">
+        <v>23</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="19">
+        <v>24</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
@@ -2474,7 +2915,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2484,20 +2925,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2759,7 +3200,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="30">
+      <c r="A31" s="24">
         <v>4</v>
       </c>
       <c r="B31" s="16" t="s">
@@ -2773,7 +3214,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="30">
+      <c r="A32" s="24">
         <v>5</v>
       </c>
       <c r="B32" s="16" t="s">
@@ -2787,7 +3228,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="30">
+      <c r="A33" s="24">
         <v>6</v>
       </c>
       <c r="B33" s="16" t="s">
@@ -2801,7 +3242,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="30">
+      <c r="A34" s="24">
         <v>7</v>
       </c>
       <c r="B34" s="16" t="s">
@@ -2815,7 +3256,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="30">
+      <c r="A35" s="24">
         <v>8</v>
       </c>
       <c r="B35" s="16" t="s">
@@ -2829,7 +3270,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="30">
+      <c r="A36" s="24">
         <v>9</v>
       </c>
       <c r="B36" s="16" t="s">
@@ -2843,7 +3284,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="30">
+      <c r="A37" s="24">
         <v>10</v>
       </c>
       <c r="B37" s="16" t="s">
@@ -2857,7 +3298,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="30">
+      <c r="A38" s="24">
         <v>11</v>
       </c>
       <c r="B38" s="16" t="s">
@@ -2871,7 +3312,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="30">
+      <c r="A39" s="24">
         <v>12</v>
       </c>
       <c r="B39" s="16" t="s">
@@ -2885,7 +3326,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="30">
+      <c r="A40" s="24">
         <v>13</v>
       </c>
       <c r="B40" s="16" t="s">
@@ -2899,7 +3340,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="30">
+      <c r="A41" s="24">
         <v>14</v>
       </c>
       <c r="B41" s="16" t="s">
@@ -2913,7 +3354,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="30">
+      <c r="A42" s="24">
         <v>15</v>
       </c>
       <c r="B42" s="16" t="s">
@@ -2923,6 +3364,146 @@
         <v>196</v>
       </c>
       <c r="D42" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="32">
+        <v>16</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="C43" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="33">
+        <v>17</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="C44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D44" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="24">
+        <v>18</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="C45" t="s">
+        <v>196</v>
+      </c>
+      <c r="D45" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="24">
+        <v>19</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="C46" t="s">
+        <v>196</v>
+      </c>
+      <c r="D46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="24">
+        <v>20</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>308</v>
+      </c>
+      <c r="C47" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="24">
+        <v>21</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="C48" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="24">
+        <v>22</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>310</v>
+      </c>
+      <c r="C49" t="s">
+        <v>196</v>
+      </c>
+      <c r="D49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="24">
+        <v>23</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="24">
+        <v>24</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="C51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="24">
+        <v>25</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>313</v>
+      </c>
+      <c r="C52" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" t="s">
         <v>196</v>
       </c>
     </row>

--- a/AI_AuditLog_Example_HoangNhatKha.xlsx
+++ b/AI_AuditLog_Example_HoangNhatKha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_UNIVERSITY\Kì 5\5.SWP391\swp391-aiauditlog-nhatkhaiphone-ux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BBBB51-C21D-44FF-8BE5-9EDB05E1625C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA812718-B8B6-4D11-8A6D-6E2826D34677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="352">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -979,6 +979,120 @@
   </si>
   <si>
     <t>Có – update profile phải whitelist field để tránh đổi role/status</t>
+  </si>
+  <si>
+    <t>Week 5 starts backend implementation for Landlord features, so the module must be separated into clear APIs and services.</t>
+  </si>
+  <si>
+    <t>Break down backend features for Landlord in RentalRoom: manage rooms, view rental requests, approve/reject requests, manage contracts, and dashboard data.</t>
+  </si>
+  <si>
+    <t>AI suggested separating LandlordRoom, RentalRequest, Contract, ViewingSchedule, PaymentSummary, and Dashboard services/routes.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI decomposition is useful but too broad for one sprint. Contextualization: Week 5 focuses on core Landlord backend only. Verification: compared with use case diagram and current database tables. Decision: implement room CRUD, rental request approval/rejection, contract creation support, and landlord dashboard summary first.</t>
+  </si>
+  <si>
+    <t>Landlord backend API plan</t>
+  </si>
+  <si>
+    <t>Landlord needs APIs to create, update, and delete room posts with images, facilities, price, address, and availability status.</t>
+  </si>
+  <si>
+    <t>Design backend validation rules and API flow for Landlord creating/updating rental room posts.</t>
+  </si>
+  <si>
+    <t>AI suggested validating required fields, price &gt; 0, area &gt; 0, address not empty, image list, facilities list, and room ownership before update/delete.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI rules are correct but image upload can be simplified for prototype. Contextualization: use image URLs or uploaded file paths depending on team implementation. Verification: checked database fields Room, RoomImage, Facility, RoomFacility. Decision: validate core room data first and handle facilities/images through separate related tables.</t>
+  </si>
+  <si>
+    <t>Room CRUD API validation notes</t>
+  </si>
+  <si>
+    <t>Landlord must review tenant rental requests and decide whether to approve or reject them before deposit payment.</t>
+  </si>
+  <si>
+    <t>Write backend flow for Landlord approving or rejecting a rental request in RentalRoom.</t>
+  </si>
+  <si>
+    <t>AI suggested: get pending requests for landlord's rooms → check request status → approve/reject → update status → notify tenant → if approved, set Pending Deposit.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI flow matches the business rule but must prevent approving invalid or already processed requests. Contextualization: landlord approval happens before tenant deposit. Verification: matched with rental request status lifecycle. Decision: allow transition only from Pending to Approved/Pending Deposit or Rejected.</t>
+  </si>
+  <si>
+    <t>Rental request approval API flow</t>
+  </si>
+  <si>
+    <t>Landlord backend APIs have a security risk if they only use roomId/requestId without checking ownership.</t>
+  </si>
+  <si>
+    <t>Check authorization risks for Landlord room and rental request APIs.</t>
+  </si>
+  <si>
+    <t>AI warned that a landlord could update another landlord's room if the API only checks login and not resource ownership.</t>
+  </si>
+  <si>
+    <t>Landlord authorization checklist</t>
+  </si>
+  <si>
+    <t>Critical Thinking: HALLUCINATION/OVERSIMPLIFICATION DETECTED: a simple role check is not enough. Contextualization: each landlord can only manage rooms they created. Verification: reviewed API parameters and database relationship User → Room. Decision: every update/delete/approve/reject query must include landlordId ownership condition.</t>
+  </si>
+  <si>
+    <t>After a tenant pays deposit, the system needs backend logic so landlord can create or confirm a rental contract correctly.</t>
+  </si>
+  <si>
+    <t>Design backend flow connecting approved request, deposit payment, and contract creation for Landlord.</t>
+  </si>
+  <si>
+    <t>AI suggested checking payment success, request status, room availability, tenant information, contract dates, deposit amount, and then creating Contract with status Active/Pending Sign.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI gave a good flow but the contract should not be created from unpaid requests. Contextualization: team rule is view room → deposit → rent room/contract. Verification: compared with Payment and Contract entities. Decision: create contract only when request is Approved/Deposited and payment is successful, then update room/status accordingly.</t>
+  </si>
+  <si>
+    <t>Contract creation backend flow</t>
+  </si>
+  <si>
+    <t>Checking only that the user role is Landlord is enough for room/request APIs.</t>
+  </si>
+  <si>
+    <t>A landlord must also own the room/request resource; otherwise one landlord may modify another landlord's data.</t>
+  </si>
+  <si>
+    <t>Reviewed API authorization logic and User → Room relationship in the database.</t>
+  </si>
+  <si>
+    <t>Add ownership checks using landlordId in update/delete/approve/reject queries.</t>
+  </si>
+  <si>
+    <t>A room only needs Available/Unavailable status after contract creation.</t>
+  </si>
+  <si>
+    <t>RentalRoom needs clearer statuses such as Available, Pending Deposit, Rented, Hidden/Inactive to handle approval, deposit, and contract flow.</t>
+  </si>
+  <si>
+    <t>Compared rental request lifecycle with room listing visibility and contract creation flow.</t>
+  </si>
+  <si>
+    <t>Update room/request status only after successful deposit and contract creation; keep listing states separated.</t>
+  </si>
+  <si>
+    <t>Có – tách landlord backend thành room/request/contract/dashboard để team dễ code</t>
+  </si>
+  <si>
+    <t>Có – validation Room API giúp tránh dữ liệu phòng thiếu giá, diện tích, địa chỉ, tiện ích</t>
+  </si>
+  <si>
+    <t>Có – approval flow đúng logic landlord duyệt trước rồi tenant mới cọc</t>
+  </si>
+  <si>
+    <t>Có – kiểm tra ownership giúp landlord không sửa phòng/yêu cầu của người khác</t>
+  </si>
+  <si>
+    <t>Có – contract chỉ tạo sau khi request/deposit hợp lệ để tránh sai nghiệp vụ</t>
   </si>
 </sst>
 </file>
@@ -1079,18 +1193,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1153,27 +1261,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1185,13 +1290,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1215,6 +1320,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1231,14 +1345,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1553,14 +1676,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1608,24 +1731,24 @@
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="16">
-        <v>140</v>
+      <c r="C10" s="15">
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="17">
-        <v>25</v>
+      <c r="C11" s="16">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.17860000000000001</v>
+      <c r="C12" s="17">
+        <v>0.17649999999999999</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>10</v>
@@ -1635,8 +1758,8 @@
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="17">
-        <v>8</v>
+      <c r="C13" s="16">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1662,7 +1785,7 @@
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>106</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -1673,30 +1796,30 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="18" t="s">
         <v>108</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1704,27 +1827,27 @@
       <c r="A20" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="18" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="15" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1733,7 +1856,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -1744,47 +1867,47 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="6">
-        <v>5</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="33">
+        <v>6</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="6">
-        <v>6</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="33">
+        <v>7</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="6">
-        <v>7</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="B26" s="33">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="6">
-        <v>7</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="B27" s="33">
+        <v>9</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1798,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1810,31 +1933,31 @@
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-    </row>
-    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+    </row>
+    <row r="3" spans="1:10" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -1860,655 +1983,841 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+    <row r="4" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="35" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+    </row>
+    <row r="5" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="37">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="35" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+    </row>
+    <row r="6" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="37">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="35" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="106.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+    </row>
+    <row r="7" spans="1:10" ht="106.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="37">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="35" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="104.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+    </row>
+    <row r="8" spans="1:10" ht="104.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="37">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="35" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="137.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+    </row>
+    <row r="9" spans="1:10" ht="137.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="37">
         <v>6</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="35" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="108.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" spans="1:10" ht="108.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="37">
         <v>7</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="35" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="89.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" spans="1:10" ht="89.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="37">
         <v>8</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="35" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="103.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" spans="1:10" ht="103.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="37">
         <v>9</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="35" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="118.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" spans="1:10" ht="118.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="37">
         <v>10</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="35" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="19">
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="35">
         <v>11</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="35" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+    </row>
+    <row r="15" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="37">
         <v>12</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="35" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+    </row>
+    <row r="16" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="37">
         <v>13</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="35" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+    </row>
+    <row r="17" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="37">
         <v>14</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="35" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+    </row>
+    <row r="18" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="37">
         <v>15</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="35" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="19">
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+    </row>
+    <row r="19" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="35">
         <v>16</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="35" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="19">
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+    </row>
+    <row r="20" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="35">
         <v>17</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="35" t="s">
         <v>248</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="35" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="19">
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+    </row>
+    <row r="21" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="35">
         <v>18</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="35" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="35" t="s">
         <v>254</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="35" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="19">
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+    </row>
+    <row r="22" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="35">
         <v>19</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="35" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="19">
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+    </row>
+    <row r="23" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="35">
         <v>20</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="35" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="19">
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+    </row>
+    <row r="24" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="35">
         <v>21</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="35" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="19">
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+    </row>
+    <row r="25" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="35">
         <v>22</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="35" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="123.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="19">
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+    </row>
+    <row r="26" spans="1:10" ht="123.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="35">
         <v>23</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="F26" s="19" t="s">
+      <c r="F26" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="35" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="31">
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+    </row>
+    <row r="27" spans="1:10" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="38">
         <v>24</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="E27" s="31" t="s">
+      <c r="E27" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="F27" s="31" t="s">
+      <c r="F27" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="H27" s="31" t="s">
+      <c r="H27" s="38" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="31">
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+    </row>
+    <row r="28" spans="1:10" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="38">
         <v>25</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="F28" s="31" t="s">
+      <c r="F28" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="38" t="s">
         <v>290</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="38" t="s">
         <v>291</v>
       </c>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+    </row>
+    <row r="29" spans="1:10" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="34">
+        <v>26</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="H29" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+    </row>
+    <row r="30" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="36">
+        <v>27</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="H30" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="I30" s="36"/>
+    </row>
+    <row r="31" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="36">
+        <v>28</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="I31" s="36"/>
+    </row>
+    <row r="32" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="36">
+        <v>29</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="E32" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="I32" s="36"/>
+    </row>
+    <row r="33" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="36">
+        <v>30</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="H33" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="I33" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2530,24 +2839,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
@@ -2573,19 +2882,19 @@
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="18" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2593,19 +2902,19 @@
       <c r="A5" s="5">
         <v>6</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>176</v>
       </c>
     </row>
@@ -2613,19 +2922,19 @@
       <c r="A6" s="5">
         <v>10</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2633,19 +2942,19 @@
       <c r="A7" s="5">
         <v>11</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>228</v>
       </c>
     </row>
@@ -2653,97 +2962,121 @@
       <c r="A8" s="5">
         <v>14</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>19</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <v>23</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19">
+      <c r="A11" s="18">
         <v>24</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+    <row r="12" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="18">
+        <v>29</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>30</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
@@ -2839,13 +3172,13 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2915,7 +3248,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2925,20 +3258,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2949,83 +3282,83 @@
       <c r="A5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="21" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="21" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="22" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="21" t="s">
         <v>187</v>
       </c>
     </row>
@@ -3038,98 +3371,98 @@
       <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>74</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="21" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="21" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="21" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3139,26 +3472,26 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
+      <c r="A28" s="6">
         <v>1</v>
       </c>
       <c r="B28" t="s">
@@ -3172,7 +3505,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
+      <c r="A29" s="6">
         <v>2</v>
       </c>
       <c r="B29" t="s">
@@ -3186,7 +3519,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <v>3</v>
       </c>
       <c r="B30" t="s">
@@ -3200,10 +3533,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="24">
+      <c r="A31" s="23">
         <v>4</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="15" t="s">
         <v>230</v>
       </c>
       <c r="C31" t="s">
@@ -3214,10 +3547,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="24">
+      <c r="A32" s="23">
         <v>5</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="15" t="s">
         <v>231</v>
       </c>
       <c r="C32" t="s">
@@ -3228,10 +3561,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="24">
+      <c r="A33" s="23">
         <v>6</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
         <v>232</v>
       </c>
       <c r="C33" t="s">
@@ -3242,10 +3575,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="24">
+      <c r="A34" s="23">
         <v>7</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="15" t="s">
         <v>233</v>
       </c>
       <c r="C34" t="s">
@@ -3256,10 +3589,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="24">
+      <c r="A35" s="23">
         <v>8</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="15" t="s">
         <v>234</v>
       </c>
       <c r="C35" t="s">
@@ -3270,10 +3603,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="24">
+      <c r="A36" s="23">
         <v>9</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="15" t="s">
         <v>235</v>
       </c>
       <c r="C36" t="s">
@@ -3284,10 +3617,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="24">
+      <c r="A37" s="23">
         <v>10</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>236</v>
       </c>
       <c r="C37" t="s">
@@ -3298,10 +3631,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="24">
+      <c r="A38" s="23">
         <v>11</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="15" t="s">
         <v>237</v>
       </c>
       <c r="C38" t="s">
@@ -3312,10 +3645,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="24">
+      <c r="A39" s="23">
         <v>12</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="15" t="s">
         <v>238</v>
       </c>
       <c r="C39" t="s">
@@ -3326,10 +3659,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="24">
+      <c r="A40" s="23">
         <v>13</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="15" t="s">
         <v>239</v>
       </c>
       <c r="C40" t="s">
@@ -3340,10 +3673,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="24">
+      <c r="A41" s="23">
         <v>14</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="15" t="s">
         <v>240</v>
       </c>
       <c r="C41" t="s">
@@ -3354,10 +3687,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="24">
+      <c r="A42" s="23">
         <v>15</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="15" t="s">
         <v>241</v>
       </c>
       <c r="C42" t="s">
@@ -3368,10 +3701,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="32">
+      <c r="A43" s="25">
         <v>16</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="24" t="s">
         <v>304</v>
       </c>
       <c r="C43" t="s">
@@ -3382,10 +3715,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="33">
+      <c r="A44" s="26">
         <v>17</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="24" t="s">
         <v>305</v>
       </c>
       <c r="C44" t="s">
@@ -3396,10 +3729,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="24">
+      <c r="A45" s="23">
         <v>18</v>
       </c>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="24" t="s">
         <v>306</v>
       </c>
       <c r="C45" t="s">
@@ -3410,10 +3743,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="24">
+      <c r="A46" s="23">
         <v>19</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="24" t="s">
         <v>307</v>
       </c>
       <c r="C46" t="s">
@@ -3424,10 +3757,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="24">
+      <c r="A47" s="23">
         <v>20</v>
       </c>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="24" t="s">
         <v>308</v>
       </c>
       <c r="C47" t="s">
@@ -3438,10 +3771,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="24">
+      <c r="A48" s="23">
         <v>21</v>
       </c>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="24" t="s">
         <v>309</v>
       </c>
       <c r="C48" t="s">
@@ -3452,10 +3785,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="24">
+      <c r="A49" s="23">
         <v>22</v>
       </c>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="24" t="s">
         <v>310</v>
       </c>
       <c r="C49" t="s">
@@ -3466,10 +3799,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="24">
+      <c r="A50" s="23">
         <v>23</v>
       </c>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="24" t="s">
         <v>311</v>
       </c>
       <c r="C50" t="s">
@@ -3480,10 +3813,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="24">
+      <c r="A51" s="23">
         <v>24</v>
       </c>
-      <c r="B51" s="31" t="s">
+      <c r="B51" s="24" t="s">
         <v>312</v>
       </c>
       <c r="C51" t="s">
@@ -3494,16 +3827,86 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="24">
+      <c r="A52" s="23">
         <v>25</v>
       </c>
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="24" t="s">
         <v>313</v>
       </c>
       <c r="C52" t="s">
         <v>196</v>
       </c>
       <c r="D52" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="23">
+        <v>26</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C53" t="s">
+        <v>196</v>
+      </c>
+      <c r="D53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="23">
+        <v>27</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C54" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="23">
+        <v>28</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="C55" t="s">
+        <v>196</v>
+      </c>
+      <c r="D55" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="23">
+        <v>29</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="C56" t="s">
+        <v>196</v>
+      </c>
+      <c r="D56" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="23">
+        <v>30</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C57" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" t="s">
         <v>196</v>
       </c>
     </row>

--- a/AI_AuditLog_Example_HoangNhatKha.xlsx
+++ b/AI_AuditLog_Example_HoangNhatKha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_UNIVERSITY\Kì 5\5.SWP391\swp391-aiauditlog-nhatkhaiphone-ux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA812718-B8B6-4D11-8A6D-6E2826D34677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C7F328-1FB3-44DB-81E4-7AC039A29A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="390">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -603,21 +603,12 @@
     <t>Critical thinking included</t>
   </si>
   <si>
-    <t>10 entries (Project range: 10-16)</t>
-  </si>
-  <si>
     <t>All 4 DTC components covered</t>
   </si>
   <si>
-    <t>3 hallucination cases</t>
-  </si>
-  <si>
     <t>Each entry has 4 reflection points</t>
   </si>
   <si>
-    <t>Evidence present for 10/10 entries</t>
-  </si>
-  <si>
     <t>Có – chia module để dễ maintain và đúng scope</t>
   </si>
   <si>
@@ -1093,6 +1084,129 @@
   </si>
   <si>
     <t>Có – contract chỉ tạo sau khi request/deposit hợp lệ để tránh sai nghiệp vụ</t>
+  </si>
+  <si>
+    <t>Week 6 starts backend implementation for Admin features, so the module needs to be separated into manageable APIs and services.</t>
+  </si>
+  <si>
+    <t>Break down backend features for Admin in RentalRoom: user management, room moderation, complaint handling, and dashboard statistics.</t>
+  </si>
+  <si>
+    <t>AI suggested UserManagement, RoomModeration, ComplaintManagement, DashboardAnalytics, and Notification services/routes.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI decomposition is suitable but some modules are too large for one sprint. Contextualization: Week 6 focuses on moderation and management functions required by Admin. Creative Synthesis: I grouped the functions into User Management, Room Moderation, Complaint Handling, and Dashboard Statistics to match project scope. Decision Ownership: I selected these modules because they directly support the Admin responsibilities defined in the SRS and use case diagram.</t>
+  </si>
+  <si>
+    <t>Admin backend module plan</t>
+  </si>
+  <si>
+    <t>Admin needs backend logic to approve, reject, or hide room listings that violate platform policies.</t>
+  </si>
+  <si>
+    <t>Design backend workflow for Admin moderating room listings in a rental room platform.</t>
+  </si>
+  <si>
+    <t>AI suggested Pending → Approved → Rejected statuses and moderation notes.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI workflow is useful but does not support removing problematic listings after approval. Contextualization: Admin may need to hide listings reported by users or found to violate platform rules. Creative Synthesis: I added Hidden status and moderation reason fields for future audits and investigations. Decision Ownership: The final workflow allows Admin to review, approve, reject, or hide room listings when necessary.</t>
+  </si>
+  <si>
+    <t>Room moderation workflow design</t>
+  </si>
+  <si>
+    <t>Admin must manage user accounts while preserving rental history and platform audit information.</t>
+  </si>
+  <si>
+    <t>Write backend logic for Admin user management including suspend, reactivate, and delete operations.</t>
+  </si>
+  <si>
+    <t>AI suggested Active, Suspended, and Deleted account statuses with role-based access control.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: The AI solution is partially correct but hard deletion may remove important rental and payment records. Contextualization: RentalRoom requires keeping historical information for dispute resolution and auditing. Creative Synthesis: I replaced permanent deletion with Soft Delete and status tracking. Decision Ownership: I selected Active, Suspended, and Soft Deleted statuses to preserve system integrity.</t>
+  </si>
+  <si>
+    <t>User management API specification</t>
+  </si>
+  <si>
+    <t>The complaint management feature requires a clear status lifecycle and handling process.</t>
+  </si>
+  <si>
+    <t>Check complaint workflow design for a rental room platform and identify missing states.</t>
+  </si>
+  <si>
+    <t>AI suggested Open, In Progress, Resolved, and Closed complaint statuses.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: HALLUCINATION/OVERSIMPLIFICATION DETECTED. AI ignored situations where complaints lack evidence or are invalid. Contextualization: Some complaints may not meet platform requirements for investigation. Creative Synthesis: I added Rejected status and Admin Resolution Notes for transparency and tracking. Decision Ownership: The updated workflow provides a more complete complaint handling process.</t>
+  </si>
+  <si>
+    <t>Complaint workflow diagram</t>
+  </si>
+  <si>
+    <t>Admin dashboard requires statistics to monitor platform activity and identify issues.</t>
+  </si>
+  <si>
+    <t>Suggest key backend APIs and metrics for an Admin dashboard in RentalRoom.</t>
+  </si>
+  <si>
+    <t>AI suggested total users, active landlords, active tenants, room listings, rental requests, complaints, and revenue statistics.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI provided useful metrics but revenue reporting is not a core requirement of the current MVP. Contextualization: RentalRoom focuses primarily on room management and rental workflows. Creative Synthesis: I prioritized user statistics, room statistics, rental requests, complaints, and moderation activities. Decision Ownership: These metrics were selected because they provide meaningful insights for system administration and monitoring.</t>
+  </si>
+  <si>
+    <t>Admin dashboard API design</t>
+  </si>
+  <si>
+    <t>User accounts can be permanently deleted when Admin removes a user.</t>
+  </si>
+  <si>
+    <t>Complaint workflow only needs Open, In Progress, Resolved, and Closed statuses.</t>
+  </si>
+  <si>
+    <t>Hard deletion may remove rental contracts, payments, complaints, and audit history needed for tracking.</t>
+  </si>
+  <si>
+    <t>Some complaints may be invalid, duplicated, spam, or unsupported due to insufficient evidence.</t>
+  </si>
+  <si>
+    <t>Reviewed User, Contract, Payment, and Complaint relationships in the database and checked data retention requirements.</t>
+  </si>
+  <si>
+    <t>Reviewed complaint handling scenarios and compared with real moderation processes.</t>
+  </si>
+  <si>
+    <t>Replaced permanent deletion with Soft Delete and account status management (Active, Suspended, Soft Deleted).</t>
+  </si>
+  <si>
+    <t>Added Rejected status and Admin Resolution Notes for better complaint tracking and transparency.</t>
+  </si>
+  <si>
+    <t>Có – chia Admin backend thành User Management, Room Moderation, Complaint Handling và Dashboard giúp module rõ ràng và dễ phát triển</t>
+  </si>
+  <si>
+    <t>Có – thêm Hidden status để Admin có thể xử lý các bài đăng vi phạm sau khi đã được duyệt</t>
+  </si>
+  <si>
+    <t>Có – sử dụng Soft Delete thay vì Hard Delete để giữ lịch sử hợp đồng, thanh toán và khiếu nại</t>
+  </si>
+  <si>
+    <t>Có – bổ sung Rejected status giúp xử lý các khiếu nại không đủ bằng chứng hoặc không hợp lệ</t>
+  </si>
+  <si>
+    <t>Có – ưu tiên thống kê người dùng, phòng trọ, yêu cầu thuê và khiếu nại thay vì tập trung vào doanh thu</t>
+  </si>
+  <si>
+    <t>35 entries</t>
+  </si>
+  <si>
+    <t>12 hallucination cases</t>
+  </si>
+  <si>
+    <t>Evidence present for 35/35 entries</t>
   </si>
 </sst>
 </file>
@@ -1261,7 +1375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1329,6 +1443,24 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1345,22 +1477,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1676,14 +1796,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1871,7 +1991,7 @@
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="27">
         <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -1882,7 +2002,7 @@
       <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="27">
         <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -1893,7 +2013,7 @@
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="33">
+      <c r="B26" s="27">
         <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -1904,7 +2024,7 @@
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="27">
         <v>9</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -1921,7 +2041,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1934,28 +2054,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="1:10" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
@@ -1984,840 +2104,970 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37">
+      <c r="A4" s="31">
         <v>1</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="37">
+      <c r="A5" s="31">
         <v>2</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
     </row>
     <row r="6" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="37">
+      <c r="A6" s="31">
         <v>3</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="7" spans="1:10" ht="106.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="37">
+      <c r="A7" s="31">
         <v>4</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="H7" s="35" t="s">
+      <c r="H7" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
     </row>
     <row r="8" spans="1:10" ht="104.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="37">
+      <c r="A8" s="31">
         <v>5</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
     </row>
     <row r="9" spans="1:10" ht="137.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="37">
+      <c r="A9" s="31">
         <v>6</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
     </row>
     <row r="10" spans="1:10" ht="108.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="37">
+      <c r="A10" s="31">
         <v>7</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
     </row>
     <row r="11" spans="1:10" ht="89.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="37">
+      <c r="A11" s="31">
         <v>8</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="35" t="s">
+      <c r="H11" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
     </row>
     <row r="12" spans="1:10" ht="103.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="37">
+      <c r="A12" s="31">
         <v>9</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="35" t="s">
+      <c r="G12" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
     </row>
     <row r="13" spans="1:10" ht="118.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="37">
+      <c r="A13" s="31">
         <v>10</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="H13" s="35" t="s">
+      <c r="H13" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
     </row>
     <row r="14" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="35">
+      <c r="A14" s="29">
         <v>11</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="H14" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+    </row>
+    <row r="15" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="31">
+        <v>12</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="G14" s="35" t="s">
+      <c r="E15" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="H14" s="35" t="s">
+      <c r="F15" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-    </row>
-    <row r="15" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="37">
-        <v>12</v>
-      </c>
-      <c r="B15" s="35" t="s">
+      <c r="G15" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+    </row>
+    <row r="16" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="31">
+        <v>13</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+    </row>
+    <row r="17" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="31">
+        <v>14</v>
+      </c>
+      <c r="B17" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C17" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+    </row>
+    <row r="18" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="31">
+        <v>15</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-    </row>
-    <row r="16" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="37">
-        <v>13</v>
-      </c>
-      <c r="B16" s="35" t="s">
+      <c r="D18" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+    </row>
+    <row r="19" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="29">
+        <v>16</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+    </row>
+    <row r="20" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="29">
+        <v>17</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+    </row>
+    <row r="21" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="29">
+        <v>18</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+    </row>
+    <row r="22" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="29">
+        <v>19</v>
+      </c>
+      <c r="B22" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C22" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+    </row>
+    <row r="23" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="29">
+        <v>20</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+    </row>
+    <row r="24" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="29">
+        <v>21</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+    </row>
+    <row r="25" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="29">
+        <v>22</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-    </row>
-    <row r="17" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="37">
-        <v>14</v>
-      </c>
-      <c r="B17" s="35" t="s">
+      <c r="D25" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>273</v>
+      </c>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+    </row>
+    <row r="26" spans="1:10" ht="123.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="29">
+        <v>23</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="H26" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+    </row>
+    <row r="27" spans="1:10" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="32">
+        <v>24</v>
+      </c>
+      <c r="B27" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C27" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="E17" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>214</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-    </row>
-    <row r="18" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="37">
-        <v>15</v>
-      </c>
-      <c r="B18" s="35" t="s">
+      <c r="D27" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+    </row>
+    <row r="28" spans="1:10" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="32">
+        <v>25</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+    </row>
+    <row r="29" spans="1:10" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="28">
+        <v>26</v>
+      </c>
+      <c r="B29" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C29" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+    </row>
+    <row r="30" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="30">
         <v>27</v>
       </c>
-      <c r="D18" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="F18" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-    </row>
-    <row r="19" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="35">
-        <v>16</v>
-      </c>
-      <c r="B19" s="35" t="s">
+      <c r="B30" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="I30" s="30"/>
+    </row>
+    <row r="31" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="30">
+        <v>28</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="E31" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="G31" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="I31" s="30"/>
+    </row>
+    <row r="32" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="30">
+        <v>29</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="G32" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="H32" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="I32" s="30"/>
+    </row>
+    <row r="33" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="30">
+        <v>30</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="G33" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="H33" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="I33" s="30"/>
+    </row>
+    <row r="34" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="39">
+        <v>31</v>
+      </c>
+      <c r="B34" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C34" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="E19" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="G19" s="35" t="s">
-        <v>245</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-    </row>
-    <row r="20" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="35">
-        <v>17</v>
-      </c>
-      <c r="B20" s="35" t="s">
+      <c r="D34" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>350</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="G34" s="40" t="s">
+        <v>352</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="39">
+        <v>32</v>
+      </c>
+      <c r="B35" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C35" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="F35" s="40" t="s">
+        <v>356</v>
+      </c>
+      <c r="G35" s="40" t="s">
+        <v>357</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="39">
+        <v>33</v>
+      </c>
+      <c r="B36" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-    </row>
-    <row r="21" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="35">
-        <v>18</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="35" t="s">
+      <c r="D36" s="40" t="s">
+        <v>359</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>360</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>361</v>
+      </c>
+      <c r="G36" s="40" t="s">
+        <v>362</v>
+      </c>
+      <c r="H36" s="40" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="39">
+        <v>34</v>
+      </c>
+      <c r="B37" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>256</v>
-      </c>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-    </row>
-    <row r="22" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="35">
-        <v>19</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="35" t="s">
+      <c r="D37" s="40" t="s">
+        <v>364</v>
+      </c>
+      <c r="E37" s="40" t="s">
+        <v>365</v>
+      </c>
+      <c r="F37" s="40" t="s">
+        <v>366</v>
+      </c>
+      <c r="G37" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="39">
+        <v>35</v>
+      </c>
+      <c r="B38" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="35" t="s">
-        <v>257</v>
-      </c>
-      <c r="E22" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="F22" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="H22" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-    </row>
-    <row r="23" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="35">
-        <v>20</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="E23" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="G23" s="35" t="s">
-        <v>265</v>
-      </c>
-      <c r="H23" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-    </row>
-    <row r="24" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="35">
-        <v>21</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="E24" s="35" t="s">
-        <v>268</v>
-      </c>
-      <c r="F24" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="G24" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="H24" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-    </row>
-    <row r="25" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="35">
-        <v>22</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="E25" s="35" t="s">
-        <v>273</v>
-      </c>
-      <c r="F25" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="G25" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>276</v>
-      </c>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-    </row>
-    <row r="26" spans="1:10" ht="123.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="35">
-        <v>23</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="35" t="s">
-        <v>277</v>
-      </c>
-      <c r="E26" s="35" t="s">
-        <v>278</v>
-      </c>
-      <c r="F26" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="H26" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-    </row>
-    <row r="27" spans="1:10" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="38">
-        <v>24</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-    </row>
-    <row r="28" spans="1:10" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="38">
-        <v>25</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>291</v>
-      </c>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-    </row>
-    <row r="29" spans="1:10" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="34">
-        <v>26</v>
-      </c>
-      <c r="B29" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="E29" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="F29" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="G29" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="H29" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-    </row>
-    <row r="30" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="36">
-        <v>27</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="E30" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="G30" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="H30" s="38" t="s">
-        <v>323</v>
-      </c>
-      <c r="I30" s="36"/>
-    </row>
-    <row r="31" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="36">
-        <v>28</v>
-      </c>
-      <c r="B31" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>328</v>
-      </c>
-      <c r="I31" s="36"/>
-    </row>
-    <row r="32" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="36">
-        <v>29</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>329</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>331</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>333</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>332</v>
-      </c>
-      <c r="I32" s="36"/>
-    </row>
-    <row r="33" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="36">
-        <v>30</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="E33" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>336</v>
-      </c>
-      <c r="G33" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="H33" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="I33" s="36"/>
+      <c r="D38" s="40" t="s">
+        <v>369</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>370</v>
+      </c>
+      <c r="F38" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="G38" s="40" t="s">
+        <v>372</v>
+      </c>
+      <c r="H38" s="40" t="s">
+        <v>373</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2839,24 +3089,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
@@ -2946,16 +3196,16 @@
         <v>67</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2966,16 +3216,16 @@
         <v>58</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2986,16 +3236,16 @@
         <v>58</v>
       </c>
       <c r="C9" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="E9" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="F9" s="18" t="s">
         <v>298</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3006,16 +3256,16 @@
         <v>58</v>
       </c>
       <c r="C10" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="E10" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="F10" s="18" t="s">
         <v>299</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3026,16 +3276,16 @@
         <v>61</v>
       </c>
       <c r="C11" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="E11" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="F11" s="18" t="s">
         <v>300</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3046,16 +3296,16 @@
         <v>58</v>
       </c>
       <c r="C12" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>339</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3066,33 +3316,57 @@
         <v>58</v>
       </c>
       <c r="C13" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="F13" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>346</v>
-      </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="A14" s="5">
+        <v>33</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="A15" s="5">
+        <v>34</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
@@ -3248,7 +3522,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3258,20 +3532,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3392,7 +3666,7 @@
         <v>182</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>188</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3406,7 +3680,7 @@
         <v>182</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3420,7 +3694,7 @@
         <v>182</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>190</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3434,7 +3708,7 @@
         <v>182</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3448,7 +3722,7 @@
         <v>182</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>192</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -3495,13 +3769,13 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D28" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -3509,13 +3783,13 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -3523,13 +3797,13 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D30" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -3537,13 +3811,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C31" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D31" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -3551,13 +3825,13 @@
         <v>5</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -3565,13 +3839,13 @@
         <v>6</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C33" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D33" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -3579,13 +3853,13 @@
         <v>7</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C34" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D34" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -3593,13 +3867,13 @@
         <v>8</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C35" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D35" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -3607,13 +3881,13 @@
         <v>9</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C36" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D36" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -3621,13 +3895,13 @@
         <v>10</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C37" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D37" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -3635,13 +3909,13 @@
         <v>11</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -3649,13 +3923,13 @@
         <v>12</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C39" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -3663,13 +3937,13 @@
         <v>13</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C40" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D40" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -3677,13 +3951,13 @@
         <v>14</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D41" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -3691,13 +3965,13 @@
         <v>15</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D42" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -3705,13 +3979,13 @@
         <v>16</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D43" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -3719,13 +3993,13 @@
         <v>17</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C44" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D44" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -3733,13 +4007,13 @@
         <v>18</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C45" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D45" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -3747,13 +4021,13 @@
         <v>19</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C46" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D46" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -3761,13 +4035,13 @@
         <v>20</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D47" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -3775,13 +4049,13 @@
         <v>21</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -3789,13 +4063,13 @@
         <v>22</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C49" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D49" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -3803,13 +4077,13 @@
         <v>23</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D50" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -3817,13 +4091,13 @@
         <v>24</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D51" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -3831,13 +4105,13 @@
         <v>25</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C52" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D52" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -3845,13 +4119,13 @@
         <v>26</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C53" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -3859,13 +4133,13 @@
         <v>27</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C54" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D54" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -3873,13 +4147,13 @@
         <v>28</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C55" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D55" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -3887,13 +4161,13 @@
         <v>29</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -3901,13 +4175,83 @@
         <v>30</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C57" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D57" t="s">
-        <v>196</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="23">
+        <v>31</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C58" t="s">
+        <v>193</v>
+      </c>
+      <c r="D58" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="23">
+        <v>32</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="C59" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="23">
+        <v>33</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="C60" t="s">
+        <v>193</v>
+      </c>
+      <c r="D60" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="23">
+        <v>34</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="C61" t="s">
+        <v>193</v>
+      </c>
+      <c r="D61" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="23">
+        <v>35</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="C62" t="s">
+        <v>193</v>
+      </c>
+      <c r="D62" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/AI_AuditLog_Example_HoangNhatKha.xlsx
+++ b/AI_AuditLog_Example_HoangNhatKha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_UNIVERSITY\Kì 5\5.SWP391\swp391-aiauditlog-nhatkhaiphone-ux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C7F328-1FB3-44DB-81E4-7AC039A29A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45943F7-64DB-4694-9F51-65A004C798D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="433">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1200,20 +1200,149 @@
     <t>Có – ưu tiên thống kê người dùng, phòng trọ, yêu cầu thuê và khiếu nại thay vì tập trung vào doanh thu</t>
   </si>
   <si>
-    <t>35 entries</t>
-  </si>
-  <si>
     <t>12 hallucination cases</t>
   </si>
   <si>
-    <t>Evidence present for 35/35 entries</t>
+    <t>Tenant Frontend - Room Search</t>
+  </si>
+  <si>
+    <t>Need to build a room search interface with multi-condition filters (price, area, location) that is highly responsive on mobile devices.</t>
+  </si>
+  <si>
+    <t>"Write a React component to filter rental rooms with multiple criteria (price range, area). Require a responsive UI with a collapsible sidebar on mobile using Tailwind CSS."</t>
+  </si>
+  <si>
+    <t>AI provided code using useState to manage the sidebar toggle and used Tailwind classes (hidden, md:block) for responsiveness, along with basic client-side array filtering logic.</t>
+  </si>
+  <si>
+    <t>AI code only filtered on the frontend. I decided to change this approach: moved the filtering logic to the Backend via Query Params to optimize performance, and added a useDebounce hook to prevent continuous API calls while the user is typing the price.</t>
+  </si>
+  <si>
+    <t>SearchRoom.jsx file uses useDebounce and passes query parameters to fetch data instead of filtering a static array.</t>
+  </si>
+  <si>
+    <t>Tenant Frontend - Room Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Tenant Backend - Booking Flow</t>
+  </si>
+  <si>
+    <t>Tenant Frontend - Booking UI</t>
+  </si>
+  <si>
+    <t>Tenant Backend - Complaint System</t>
+  </si>
+  <si>
+    <t>Need to display the room details page including an image carousel, description, and landlord info, while properly handling loading and error states.</t>
+  </si>
+  <si>
+    <t>When a tenant initiates a deposit, if they do not pay within 24 hours, the system must automatically cancel the pending reservation to allow others to rent.</t>
+  </si>
+  <si>
+    <t>The booking form requires the tenant to enter a lot of information, review terms, and confirm payment. Putting it all on one long page would overwhelm the user.</t>
+  </si>
+  <si>
+    <t>Tenants need to submit complaints (e.g., broken furniture). It needs an image upload flow for evidence and the ability to track resolution statuses.</t>
+  </si>
+  <si>
+    <t>"How to fetch and display rental room details, including an image slider library and landlord information, with loading/error state handling in React?"</t>
+  </si>
+  <si>
+    <t>"Write backend logic (Node.js) for room booking deposits. The 'Pending Deposit' status must automatically expire after 24 hours if the user does not transfer the money."</t>
+  </si>
+  <si>
+    <t>"Design a multi-step modal booking form in React: Step 1: Review details; Step 2: Confirm information; Step 3: Upload payment receipt."</t>
+  </si>
+  <si>
+    <t>"Write an API to create a complaint for a Tenant, including uploading evidence images and having Open, In Progress, Resolved statuses."</t>
+  </si>
+  <si>
+    <t>AI suggested writing the API fetch function directly inside the useEffect of the RoomDetails component and using the react-responsive-carousel library for the slider.</t>
+  </si>
+  <si>
+    <t>AI suggested adding an expirationDate field to the Booking table and recommended using node-cron to run a scheduled job every minute/hour.</t>
+  </si>
+  <si>
+    <t>AI created a giant component containing 3 if/else blocks to render all steps based on a single currentStep state variable.</t>
+  </si>
+  <si>
+    <t>AI provided a basic RESTful API using the multer library to upload images and save them directly to the local public/uploads folder on the server.</t>
+  </si>
+  <si>
+    <t>Putting API logic directly in the UI component makes it messy and hard to maintain. I refactored it by creating a custom hook useFetchRoomDetails to separate the data fetching logic (Abstraction). The UI component only receives and renders data.</t>
+  </si>
+  <si>
+    <t>Using a cron job to scan the entire DB continuously consumes heavy resources. I changed the algorithm: I implemented BullMQ's Delayed Job feature to handle the expiration exactly 24 hours later, which is much more optimized.</t>
+  </si>
+  <si>
+    <t>The AI code was too long and hard to scale/maintain. I broke it down (Decompose) into 3 completely separate child components: ReviewStep, ConfirmStep, and PaymentStep, managed via a parent BookingStepper wrapper.</t>
+  </si>
+  <si>
+    <t>Saving images locally will cause them to be lost when deploying to a cloud host. I modified the AI code to store images on Cloudinary. I also manually added a "Rejected" status to the Schema for invalid/fake complaints.</t>
+  </si>
+  <si>
+    <t>hooks/useFetchRoomDetails.js contains the separated API logic, making the RoomDetails.jsx component much cleaner.</t>
+  </si>
+  <si>
+    <t>Expiration logic in BookingService.js uses BullMQ delayed queues instead of node-cron scanning the whole database.</t>
+  </si>
+  <si>
+    <t>Folder structure components/BookingSteps consists of independent child component files rather than everything being grouped into one massive file.</t>
+  </si>
+  <si>
+    <t>ComplaintController.js integrates the Cloudinary SDK, and the MongoDB/SQL Schema includes a "Rejected" Enum.</t>
+  </si>
+  <si>
+    <t>AI suggested sending the minPrice and maxPrice filter parameters via the body of an HTTP GET request in the Room Search feature.</t>
+  </si>
+  <si>
+    <t>The HTTP GET method should not contain a body. Search parameters must be passed via URL parameters (Query String).</t>
+  </si>
+  <si>
+    <t>Testing the API from the Frontend resulted in a 400 Bad Request error, or the API returned all rooms because the backend ignored the GET body.</t>
+  </si>
+  <si>
+    <t>Changed the data fetching method on the frontend, passing the filter parameters as a query string ?minPrice=X&amp;maxPrice=Y in the URL.</t>
+  </si>
+  <si>
+    <t>AI generated the flow: When the tenant clicks "Book Room", the system immediately changes the room status to "Rented".</t>
+  </si>
+  <si>
+    <t>In reality, the business logic requires a "Pending Deposit" step to wait for deposit payment. Changing it immediately to "Rented" violates the workflow.</t>
+  </si>
+  <si>
+    <t>Compared the AI-generated code flow with the SRS document and the approved Use Case diagram (deposit payment is mandatory).</t>
+  </si>
+  <si>
+    <t>Updated the flow: Set the status to "Pending Deposit" first, and only change it to "Rented" after the deposit payment is successfully confirmed.</t>
+  </si>
+  <si>
+    <t>40 entries</t>
+  </si>
+  <si>
+    <t>Evidence present for 40/40 entries</t>
+  </si>
+  <si>
+    <t>Có – chuyển logic filter xuống backend và dùng debounce giúp tăng hiệu năng, tránh gọi API liên tục</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Có – tách API fetching ra custom hook giúp component UI gọn gàng, dễ tái sử dụng và bảo trì</t>
+  </si>
+  <si>
+    <t>Có – dùng background job (BullMQ) để tự động huỷ cọc thay vì quét toàn bộ DB giúp tối ưu tài nguyên server</t>
+  </si>
+  <si>
+    <t>Có – chia nhỏ form đặt phòng phức tạp thành nhiều bước (multi-step) giúp UX thân thiện, người thuê không bị ngợp</t>
+  </si>
+  <si>
+    <t>Có – lưu ảnh minh chứng lên Cloudinary để không mất data khi deploy, đồng thời thêm trạng thái Rejected để loại bỏ khiếu nại ảo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1375,7 +1504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1461,6 +1590,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1476,12 +1612,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1786,7 +1916,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1795,22 +1925,22 @@
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-    </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+    </row>
+    <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1818,7 +1948,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1826,7 +1956,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1834,7 +1964,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1842,52 +1972,52 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="18">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="15">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="16">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="17">
-        <v>0.17649999999999999</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="15" thickBot="1">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
@@ -1901,7 +2031,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="29.4" thickBot="1">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -1915,7 +2045,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="29.4" thickBot="1">
       <c r="A18" s="18" t="s">
         <v>20</v>
       </c>
@@ -1929,7 +2059,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="29.4" thickBot="1">
       <c r="A19" s="18" t="s">
         <v>110</v>
       </c>
@@ -1943,7 +2073,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="29.4" thickBot="1">
       <c r="A20" s="5" t="s">
         <v>113</v>
       </c>
@@ -1957,7 +2087,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="28.8">
       <c r="A21" s="15" t="s">
         <v>117</v>
       </c>
@@ -1971,12 +2101,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="15" thickBot="1">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
@@ -1987,45 +2117,45 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="15" thickBot="1">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B24" s="27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="15" thickBot="1">
       <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="15" thickBot="1">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="15" thickBot="1">
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="27">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>26</v>
@@ -2041,8 +2171,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -2053,31 +2183,31 @@
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1">
+      <c r="A2" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-    </row>
-    <row r="3" spans="1:10" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+    </row>
+    <row r="3" spans="1:10" ht="40.049999999999997" customHeight="1" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -2103,7 +2233,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="100.05" customHeight="1" thickBot="1">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -2131,7 +2261,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="100.05" customHeight="1" thickBot="1">
       <c r="A5" s="31">
         <v>2</v>
       </c>
@@ -2159,7 +2289,7 @@
       <c r="I5" s="30"/>
       <c r="J5" s="30"/>
     </row>
-    <row r="6" spans="1:10" ht="100.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="100.05" customHeight="1" thickBot="1">
       <c r="A6" s="31">
         <v>3</v>
       </c>
@@ -2187,7 +2317,7 @@
       <c r="I6" s="30"/>
       <c r="J6" s="30"/>
     </row>
-    <row r="7" spans="1:10" ht="106.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="106.2" customHeight="1" thickBot="1">
       <c r="A7" s="31">
         <v>4</v>
       </c>
@@ -2215,7 +2345,7 @@
       <c r="I7" s="30"/>
       <c r="J7" s="30"/>
     </row>
-    <row r="8" spans="1:10" ht="104.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="104.4" customHeight="1" thickBot="1">
       <c r="A8" s="31">
         <v>5</v>
       </c>
@@ -2243,7 +2373,7 @@
       <c r="I8" s="30"/>
       <c r="J8" s="30"/>
     </row>
-    <row r="9" spans="1:10" ht="137.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="137.4" customHeight="1" thickBot="1">
       <c r="A9" s="31">
         <v>6</v>
       </c>
@@ -2271,7 +2401,7 @@
       <c r="I9" s="30"/>
       <c r="J9" s="30"/>
     </row>
-    <row r="10" spans="1:10" ht="108.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="108.6" customHeight="1" thickBot="1">
       <c r="A10" s="31">
         <v>7</v>
       </c>
@@ -2299,7 +2429,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="1:10" ht="89.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="89.4" customHeight="1" thickBot="1">
       <c r="A11" s="31">
         <v>8</v>
       </c>
@@ -2327,7 +2457,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="1:10" ht="103.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="103.8" customHeight="1" thickBot="1">
       <c r="A12" s="31">
         <v>9</v>
       </c>
@@ -2355,7 +2485,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="1:10" ht="118.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="118.2" customHeight="1" thickBot="1">
       <c r="A13" s="31">
         <v>10</v>
       </c>
@@ -2383,7 +2513,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A14" s="29">
         <v>11</v>
       </c>
@@ -2411,7 +2541,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A15" s="31">
         <v>12</v>
       </c>
@@ -2439,7 +2569,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A16" s="31">
         <v>13</v>
       </c>
@@ -2467,7 +2597,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A17" s="31">
         <v>14</v>
       </c>
@@ -2495,7 +2625,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A18" s="31">
         <v>15</v>
       </c>
@@ -2523,7 +2653,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A19" s="29">
         <v>16</v>
       </c>
@@ -2551,7 +2681,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A20" s="29">
         <v>17</v>
       </c>
@@ -2579,7 +2709,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A21" s="29">
         <v>18</v>
       </c>
@@ -2607,7 +2737,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A22" s="29">
         <v>19</v>
       </c>
@@ -2635,7 +2765,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A23" s="29">
         <v>20</v>
       </c>
@@ -2663,7 +2793,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A24" s="29">
         <v>21</v>
       </c>
@@ -2691,7 +2821,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10" ht="79.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="79.95" customHeight="1" thickBot="1">
       <c r="A25" s="29">
         <v>22</v>
       </c>
@@ -2719,7 +2849,7 @@
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="1:10" ht="123.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" ht="123.6" customHeight="1" thickBot="1">
       <c r="A26" s="29">
         <v>23</v>
       </c>
@@ -2747,7 +2877,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
     </row>
-    <row r="27" spans="1:10" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="104.4" customHeight="1">
       <c r="A27" s="32">
         <v>24</v>
       </c>
@@ -2775,7 +2905,7 @@
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
     </row>
-    <row r="28" spans="1:10" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="66" customHeight="1" thickBot="1">
       <c r="A28" s="32">
         <v>25</v>
       </c>
@@ -2803,7 +2933,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
     </row>
-    <row r="29" spans="1:10" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="101.4" thickBot="1">
       <c r="A29" s="28">
         <v>26</v>
       </c>
@@ -2831,7 +2961,7 @@
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
     </row>
-    <row r="30" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="100.8">
       <c r="A30" s="30">
         <v>27</v>
       </c>
@@ -2858,7 +2988,7 @@
       </c>
       <c r="I30" s="30"/>
     </row>
-    <row r="31" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="86.4">
       <c r="A31" s="30">
         <v>28</v>
       </c>
@@ -2885,7 +3015,7 @@
       </c>
       <c r="I31" s="30"/>
     </row>
-    <row r="32" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="100.8">
       <c r="A32" s="30">
         <v>29</v>
       </c>
@@ -2912,7 +3042,7 @@
       </c>
       <c r="I32" s="30"/>
     </row>
-    <row r="33" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="100.8">
       <c r="A33" s="30">
         <v>30</v>
       </c>
@@ -2939,134 +3069,264 @@
       </c>
       <c r="I33" s="30"/>
     </row>
-    <row r="34" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="39">
+    <row r="34" spans="1:9" ht="129.6">
+      <c r="A34" s="34">
         <v>31</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="40" t="s">
+      <c r="D34" s="35" t="s">
         <v>349</v>
       </c>
-      <c r="E34" s="40" t="s">
+      <c r="E34" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="F34" s="40" t="s">
+      <c r="F34" s="35" t="s">
         <v>351</v>
       </c>
-      <c r="G34" s="40" t="s">
+      <c r="G34" s="35" t="s">
         <v>352</v>
       </c>
-      <c r="H34" s="40" t="s">
+      <c r="H34" s="35" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="39">
+    <row r="35" spans="1:9" ht="115.2">
+      <c r="A35" s="34">
         <v>32</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="40" t="s">
+      <c r="C35" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="40" t="s">
+      <c r="D35" s="35" t="s">
         <v>354</v>
       </c>
-      <c r="E35" s="40" t="s">
+      <c r="E35" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="F35" s="40" t="s">
+      <c r="F35" s="35" t="s">
         <v>356</v>
       </c>
-      <c r="G35" s="40" t="s">
+      <c r="G35" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="H35" s="40" t="s">
+      <c r="H35" s="35" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="39">
+    <row r="36" spans="1:9" ht="115.2">
+      <c r="A36" s="34">
         <v>33</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="40" t="s">
+      <c r="D36" s="35" t="s">
         <v>359</v>
       </c>
-      <c r="E36" s="40" t="s">
+      <c r="E36" s="35" t="s">
         <v>360</v>
       </c>
-      <c r="F36" s="40" t="s">
+      <c r="F36" s="35" t="s">
         <v>361</v>
       </c>
-      <c r="G36" s="40" t="s">
+      <c r="G36" s="35" t="s">
         <v>362</v>
       </c>
-      <c r="H36" s="40" t="s">
+      <c r="H36" s="35" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="39">
+    <row r="37" spans="1:9" ht="115.2">
+      <c r="A37" s="34">
         <v>34</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="D37" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="E37" s="35" t="s">
         <v>365</v>
       </c>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="35" t="s">
         <v>366</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="G37" s="35" t="s">
         <v>367</v>
       </c>
-      <c r="H37" s="40" t="s">
+      <c r="H37" s="35" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39">
+    <row r="38" spans="1:9" ht="129.6">
+      <c r="A38" s="34">
         <v>35</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="40" t="s">
+      <c r="D38" s="35" t="s">
         <v>369</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="35" t="s">
         <v>370</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="F38" s="35" t="s">
         <v>371</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="35" t="s">
         <v>372</v>
       </c>
-      <c r="H38" s="40" t="s">
+      <c r="H38" s="35" t="s">
         <v>373</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="86.4">
+      <c r="A39" s="34">
+        <v>36</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>388</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>389</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>390</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>391</v>
+      </c>
+      <c r="G39" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="100.8">
+      <c r="A40" s="34">
+        <v>37</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="D40" s="35" t="s">
+        <v>398</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>402</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>406</v>
+      </c>
+      <c r="G40" s="35" t="s">
+        <v>410</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="86.4">
+      <c r="A41" s="34">
+        <v>38</v>
+      </c>
+      <c r="B41" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="D41" s="35" t="s">
+        <v>399</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>403</v>
+      </c>
+      <c r="F41" s="35" t="s">
+        <v>407</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>411</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="115.2">
+      <c r="A42" s="34">
+        <v>39</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>396</v>
+      </c>
+      <c r="D42" s="35" t="s">
+        <v>400</v>
+      </c>
+      <c r="E42" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="F42" s="35" t="s">
+        <v>408</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="86.4">
+      <c r="A43" s="34">
+        <v>40</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>397</v>
+      </c>
+      <c r="D43" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>405</v>
+      </c>
+      <c r="F43" s="35" t="s">
+        <v>409</v>
+      </c>
+      <c r="G43" s="35" t="s">
+        <v>413</v>
+      </c>
+      <c r="H43" s="35" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -3081,34 +3341,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-    </row>
-    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+    </row>
+    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>45</v>
       </c>
@@ -3128,7 +3388,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -3148,7 +3408,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="43.8" thickBot="1">
       <c r="A5" s="5">
         <v>6</v>
       </c>
@@ -3168,7 +3428,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A6" s="5">
         <v>10</v>
       </c>
@@ -3188,7 +3448,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A7" s="5">
         <v>11</v>
       </c>
@@ -3208,7 +3468,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A8" s="5">
         <v>14</v>
       </c>
@@ -3228,7 +3488,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A9" s="18">
         <v>19</v>
       </c>
@@ -3248,7 +3508,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A10" s="18">
         <v>23</v>
       </c>
@@ -3268,7 +3528,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A11" s="18">
         <v>24</v>
       </c>
@@ -3288,7 +3548,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A12" s="18">
         <v>29</v>
       </c>
@@ -3308,7 +3568,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="60" customHeight="1" thickBot="1">
       <c r="A13" s="5">
         <v>30</v>
       </c>
@@ -3328,7 +3588,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="60" customHeight="1">
       <c r="A14" s="5">
         <v>33</v>
       </c>
@@ -3348,7 +3608,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="60" customHeight="1">
       <c r="A15" s="5">
         <v>34</v>
       </c>
@@ -3368,23 +3628,47 @@
         <v>381</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="60" customHeight="1">
+      <c r="A16" s="5">
+        <v>36</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="60" customHeight="1">
+      <c r="A17" s="5">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="60" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -3392,7 +3676,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="60" customHeight="1">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -3400,7 +3684,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="60" customHeight="1">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -3408,7 +3692,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="60" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -3416,7 +3700,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="60" customHeight="1">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -3424,7 +3708,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="60" customHeight="1">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3432,7 +3716,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="60" customHeight="1">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -3440,12 +3724,12 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
-    <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="7" t="s">
         <v>53</v>
       </c>
@@ -3456,7 +3740,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="28.8">
       <c r="A32" s="5" t="s">
         <v>51</v>
       </c>
@@ -3467,7 +3751,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="28.8">
       <c r="A33" s="5" t="s">
         <v>58</v>
       </c>
@@ -3478,7 +3762,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="28.8">
       <c r="A34" s="5" t="s">
         <v>61</v>
       </c>
@@ -3489,7 +3773,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="28.8">
       <c r="A35" s="5" t="s">
         <v>64</v>
       </c>
@@ -3500,7 +3784,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="43.2">
       <c r="A36" s="5" t="s">
         <v>67</v>
       </c>
@@ -3522,8 +3806,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D67"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -3531,28 +3815,28 @@
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-    </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+    </row>
+    <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="15" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>73</v>
       </c>
@@ -3566,7 +3850,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="15" thickBot="1">
       <c r="A6" s="9" t="s">
         <v>77</v>
       </c>
@@ -3580,7 +3864,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="28.2" thickBot="1">
       <c r="A7" s="9" t="s">
         <v>79</v>
       </c>
@@ -3594,7 +3878,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="15" thickBot="1">
       <c r="A8" s="9" t="s">
         <v>81</v>
       </c>
@@ -3608,7 +3892,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="15" thickBot="1">
       <c r="A9" s="9" t="s">
         <v>83</v>
       </c>
@@ -3622,7 +3906,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="15" thickBot="1">
       <c r="A10" s="9" t="s">
         <v>85</v>
       </c>
@@ -3636,12 +3920,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="18">
       <c r="A12" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="15" thickBot="1">
       <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
@@ -3655,7 +3939,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="15" thickBot="1">
       <c r="A14" s="9" t="s">
         <v>77</v>
       </c>
@@ -3666,10 +3950,10 @@
         <v>182</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1">
       <c r="A15" s="9" t="s">
         <v>79</v>
       </c>
@@ -3683,7 +3967,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="15" thickBot="1">
       <c r="A16" s="9" t="s">
         <v>81</v>
       </c>
@@ -3694,10 +3978,10 @@
         <v>182</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1">
       <c r="A17" s="9" t="s">
         <v>83</v>
       </c>
@@ -3711,7 +3995,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="15" thickBot="1">
       <c r="A18" s="9" t="s">
         <v>85</v>
       </c>
@@ -3722,35 +4006,35 @@
         <v>182</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="43.2">
       <c r="A27" s="14" t="s">
         <v>32</v>
       </c>
@@ -3764,7 +4048,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" s="6">
         <v>1</v>
       </c>
@@ -3778,7 +4062,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29" s="6">
         <v>2</v>
       </c>
@@ -3792,7 +4076,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30" s="6">
         <v>3</v>
       </c>
@@ -3806,7 +4090,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31" s="23">
         <v>4</v>
       </c>
@@ -3820,7 +4104,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="28.8">
       <c r="A32" s="23">
         <v>5</v>
       </c>
@@ -3834,7 +4118,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33" s="23">
         <v>6</v>
       </c>
@@ -3848,7 +4132,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34" s="23">
         <v>7</v>
       </c>
@@ -3862,7 +4146,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35" s="23">
         <v>8</v>
       </c>
@@ -3876,7 +4160,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36" s="23">
         <v>9</v>
       </c>
@@ -3890,7 +4174,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37" s="23">
         <v>10</v>
       </c>
@@ -3904,7 +4188,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="A38" s="23">
         <v>11</v>
       </c>
@@ -3918,7 +4202,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39" s="23">
         <v>12</v>
       </c>
@@ -3932,7 +4216,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40" s="23">
         <v>13</v>
       </c>
@@ -3946,7 +4230,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41" s="23">
         <v>14</v>
       </c>
@@ -3960,7 +4244,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42" s="23">
         <v>15</v>
       </c>
@@ -3974,7 +4258,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="28.8">
       <c r="A43" s="25">
         <v>16</v>
       </c>
@@ -3988,7 +4272,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44" s="26">
         <v>17</v>
       </c>
@@ -4002,7 +4286,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45" s="23">
         <v>18</v>
       </c>
@@ -4016,7 +4300,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="A46" s="23">
         <v>19</v>
       </c>
@@ -4030,7 +4314,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47" s="23">
         <v>20</v>
       </c>
@@ -4044,7 +4328,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4">
       <c r="A48" s="23">
         <v>21</v>
       </c>
@@ -4058,7 +4342,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49" s="23">
         <v>22</v>
       </c>
@@ -4072,7 +4356,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4">
       <c r="A50" s="23">
         <v>23</v>
       </c>
@@ -4086,7 +4370,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4">
       <c r="A51" s="23">
         <v>24</v>
       </c>
@@ -4100,7 +4384,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4">
       <c r="A52" s="23">
         <v>25</v>
       </c>
@@ -4114,7 +4398,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="28.8">
       <c r="A53" s="23">
         <v>26</v>
       </c>
@@ -4128,7 +4412,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="28.8">
       <c r="A54" s="23">
         <v>27</v>
       </c>
@@ -4142,7 +4426,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="A55" s="23">
         <v>28</v>
       </c>
@@ -4156,7 +4440,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="28.8">
       <c r="A56" s="23">
         <v>29</v>
       </c>
@@ -4170,7 +4454,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="A57" s="23">
         <v>30</v>
       </c>
@@ -4184,7 +4468,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="28.8">
       <c r="A58" s="23">
         <v>31</v>
       </c>
@@ -4198,7 +4482,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="28.8">
       <c r="A59" s="23">
         <v>32</v>
       </c>
@@ -4212,7 +4496,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="28.8">
       <c r="A60" s="23">
         <v>33</v>
       </c>
@@ -4226,7 +4510,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="28.8">
       <c r="A61" s="23">
         <v>34</v>
       </c>
@@ -4240,7 +4524,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" ht="28.8">
       <c r="A62" s="23">
         <v>35</v>
       </c>
@@ -4251,6 +4535,76 @@
         <v>193</v>
       </c>
       <c r="D62" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="28.8">
+      <c r="A63" s="23">
+        <v>36</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="C63" t="s">
+        <v>193</v>
+      </c>
+      <c r="D63" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="28.8">
+      <c r="A64" s="23">
+        <v>37</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C64" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="D64" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="28.8">
+      <c r="A65" s="23">
+        <v>38</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="C65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="28.8">
+      <c r="A66" s="23">
+        <v>39</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="C66" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="D66" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="28.8">
+      <c r="A67" s="23">
+        <v>40</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C67" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="D67" s="33" t="s">
         <v>193</v>
       </c>
     </row>

--- a/AI_AuditLog_Example_HoangNhatKha.xlsx
+++ b/AI_AuditLog_Example_HoangNhatKha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_UNIVERSITY\Kì 5\5.SWP391\swp391-aiauditlog-nhatkhaiphone-ux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45943F7-64DB-4694-9F51-65A004C798D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083757D9-BCA7-4CBE-B7A4-CB0DEC3F536C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="471">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1200,9 +1200,6 @@
     <t>Có – ưu tiên thống kê người dùng, phòng trọ, yêu cầu thuê và khiếu nại thay vì tập trung vào doanh thu</t>
   </si>
   <si>
-    <t>12 hallucination cases</t>
-  </si>
-  <si>
     <t>Tenant Frontend - Room Search</t>
   </si>
   <si>
@@ -1317,12 +1314,6 @@
     <t>Updated the flow: Set the status to "Pending Deposit" first, and only change it to "Rented" after the deposit payment is successfully confirmed.</t>
   </si>
   <si>
-    <t>40 entries</t>
-  </si>
-  <si>
-    <t>Evidence present for 40/40 entries</t>
-  </si>
-  <si>
     <t>Có – chuyển logic filter xuống backend và dùng debounce giúp tăng hiệu năng, tránh gọi API liên tục</t>
   </si>
   <si>
@@ -1336,6 +1327,129 @@
   </si>
   <si>
     <t>Có – lưu ảnh minh chứng lên Cloudinary để không mất data khi deploy, đồng thời thêm trạng thái Rejected để loại bỏ khiếu nại ảo</t>
+  </si>
+  <si>
+    <t>Sửa lỗi 404 khi Landlord duyệt phòng</t>
+  </si>
+  <si>
+    <t>Refactor Messages từ Mock Data sang API</t>
+  </si>
+  <si>
+    <t>"When a landlord clicks approve rental request, the frontend calls the API /api/landlord/requests/:id/approve and gets a 404 error. Please help me fix this."</t>
+  </si>
+  <si>
+    <t>Analyzed the 404 error as an incorrect route. Suggested checking the backend router file to see if the endpoint name mismatches (e.g., using rental-requests instead of requests).</t>
+  </si>
+  <si>
+    <t>Checked the backend router file and verified it was /api/landlord/rental-requests. Proceeded to fix the frontend fetch URL to match the backend.</t>
+  </si>
+  <si>
+    <t>API approve/reject request connects successfully, and data updates correctly.</t>
+  </si>
+  <si>
+    <t>"I am using mock data for the Messages page. Provide the logic to create a custom hook useConversations that calls the actual API whenever a user selects a chat."</t>
+  </si>
+  <si>
+    <t>Provided code using useEffect to fetch data from /api/landlord/conversations and /messages/:id, along with loading and error states.</t>
+  </si>
+  <si>
+    <t>Implemented the hook and removed all static mock data. Added an empty state (screen displayed when there are no messages).</t>
+  </si>
+  <si>
+    <t>Sent/received messages display correctly from the SQL Server database.</t>
+  </si>
+  <si>
+    <t>Handle Auto-scroll to bottom for chat container</t>
+  </si>
+  <si>
+    <t>Add Loading &amp; Error states for Profile</t>
+  </si>
+  <si>
+    <t>Update Check Constraint in Database</t>
+  </si>
+  <si>
+    <t>// scroll to bottom of chat container when messages array changes</t>
+  </si>
+  <si>
+    <t>"The Landlord Profile page is blank when the network is slow or the API hasn't returned data. Write a code snippet to display a loading spinner and an error fallback."</t>
+  </si>
+  <si>
+    <t>"I need to add 'Cancelled' and 'Expired' statuses for the Rental Request. Guide me on how to write an ALTER TABLE script for SQL Server to update the CHECK constraint."</t>
+  </si>
+  <si>
+    <t>Suggested using useEffect with window.scrollTo(0, document.body.scrollHeight) whenever the messages array changes.</t>
+  </si>
+  <si>
+    <t>Provided conditional rendering logic: if (isLoading) return &lt;Spinner /&gt; and if (error) return &lt;Alert&gt;Error&lt;/Alert&gt;.</t>
+  </si>
+  <si>
+    <t>Provided the command ALTER TABLE ... DROP CONSTRAINT and ADD CONSTRAINT ... CHECK (Status IN ('Pending', 'Approved', 'Rejected', 'Cancelled', 'Expired')).</t>
+  </si>
+  <si>
+    <t>Tested and realized window.scrollTo scrolls the entire webpage (which is annoying), while I only needed to scroll the chat container.</t>
+  </si>
+  <si>
+    <t>Integrated it into the component, simulated a slow network (Slow 3G) in DevTools to test the loading state.</t>
+  </si>
+  <si>
+    <t>Executed the update script on the real DB and tried testing a Cancelled request operation to see if the database blocked invalid ones.</t>
+  </si>
+  <si>
+    <t>Switched to using useRef pointing to the last div element of the message list and called scrollIntoView({ behavior: 'smooth' }).</t>
+  </si>
+  <si>
+    <t>Smoother UX, clearly indicating to the user that the system is processing data.</t>
+  </si>
+  <si>
+    <t>The lifecycle of the Rental Request is strictly enforced and secured at the database level.</t>
+  </si>
+  <si>
+    <t>Using window.scrollTo is sufficient to scroll to the latest message in the chat box.</t>
+  </si>
+  <si>
+    <t>Suggested using a direct UPDATE command on old records to set their status to 'Pending' instead of modifying the table's CHECK Constraint.</t>
+  </si>
+  <si>
+    <t>window.scrollTo scrolls the entire browser window, shifting static layout components like the Header and Sidebar out of view.</t>
+  </si>
+  <si>
+    <t>An UPDATE command only modifies existing data. If the application code continues to insert invalid statuses, the DB will still accept them. This doesn't solve the root cause of data integrity.</t>
+  </si>
+  <si>
+    <t>Tested sending a new message and saw the entire screen jump and shift upwards unexpectedly.</t>
+  </si>
+  <si>
+    <t>Carefully read the generated SQL query and noticed the AI misunderstood the request "data constraint" as "data update".</t>
+  </si>
+  <si>
+    <t>Removed window.scrollTo, created a useRef attached to the last element of the chat container, and called scrollIntoView() instead.</t>
+  </si>
+  <si>
+    <t>Re-prompted the AI using precise keywords: "Generate a DROP CONSTRAINT and ADD CONSTRAINT CHECK script for the Status column".</t>
+  </si>
+  <si>
+    <t>45 entries</t>
+  </si>
+  <si>
+    <t>14 hallucination cases</t>
+  </si>
+  <si>
+    <t>Evidence present for 45/45 entries</t>
+  </si>
+  <si>
+    <t>Có – Việc dùng một endpoint thống nhất /api/landlord/rental-requests giúp backend dễ bảo trì route hơn và cho phép frontend xử lý triệt để được lỗi 404.</t>
+  </si>
+  <si>
+    <t>Có – Việc tách logic gọi API ra một custom hook (useConversations) giúp component React gọn gàng, dễ đọc hơn và giảm việc re-render không cần thiết.</t>
+  </si>
+  <si>
+    <t>Có – Sử dụng useRef và scrollIntoView() giúp tập trung thao tác DOM trực tiếp vào khu vực chat, thay vì làm giật/cuộn toàn bộ bố cục của trang web.</t>
+  </si>
+  <si>
+    <t>Có – Xử lý đầy đủ 3 trạng thái (Loading, Success, Error) là một tiêu chuẩn UX bắt buộc để người dùng không tưởng nhầm là trang web bị treo hay đóng băng.</t>
+  </si>
+  <si>
+    <t>Có – Sử dụng ràng buộc CHECK Constraint trực tiếp ở tầng database giúp chặn các lỗi sai trạng thái sinh ra từ tầng code, tránh việc làm hỏng dữ liệu.</t>
   </si>
 </sst>
 </file>
@@ -1982,7 +2096,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1990,7 +2104,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="16">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1998,7 +2112,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="17">
-        <v>0.17499999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>10</v>
@@ -2009,7 +2123,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="16">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18">
@@ -2122,7 +2236,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>26</v>
@@ -2133,7 +2247,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>26</v>
@@ -2144,7 +2258,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="27">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>26</v>
@@ -2155,7 +2269,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="27">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>26</v>
@@ -2171,7 +2285,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3207,22 +3321,22 @@
         <v>27</v>
       </c>
       <c r="C39" s="35" t="s">
+        <v>387</v>
+      </c>
+      <c r="D39" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="D39" s="35" t="s">
+      <c r="E39" s="35" t="s">
         <v>389</v>
       </c>
-      <c r="E39" s="35" t="s">
+      <c r="F39" s="35" t="s">
         <v>390</v>
       </c>
-      <c r="F39" s="35" t="s">
+      <c r="G39" s="35" t="s">
         <v>391</v>
       </c>
-      <c r="G39" s="35" t="s">
+      <c r="H39" s="35" t="s">
         <v>392</v>
-      </c>
-      <c r="H39" s="35" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="100.8">
@@ -3233,22 +3347,22 @@
         <v>28</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E40" s="35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G40" s="35" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H40" s="35" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="86.4">
@@ -3259,22 +3373,22 @@
         <v>29</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E41" s="35" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G41" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H41" s="35" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="115.2">
@@ -3285,22 +3399,22 @@
         <v>25</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E42" s="35" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G42" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H42" s="35" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="86.4">
@@ -3311,22 +3425,152 @@
         <v>29</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E43" s="35" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G43" s="35" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H43" s="35" t="s">
-        <v>417</v>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="86.4">
+      <c r="A44" s="34">
+        <v>41</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="D44" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="F44" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="G44" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="H44" s="35" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="86.4">
+      <c r="A45" s="34">
+        <v>42</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="D45" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>437</v>
+      </c>
+      <c r="G45" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="H45" s="35" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="86.4">
+      <c r="A46" s="34">
+        <v>43</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="D46" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>443</v>
+      </c>
+      <c r="F46" s="35" t="s">
+        <v>446</v>
+      </c>
+      <c r="G46" s="35" t="s">
+        <v>449</v>
+      </c>
+      <c r="H46" s="35" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="72">
+      <c r="A47" s="34">
+        <v>44</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>441</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="G47" s="35" t="s">
+        <v>450</v>
+      </c>
+      <c r="H47" s="35" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="86.4">
+      <c r="A48" s="34">
+        <v>45</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>442</v>
+      </c>
+      <c r="D48" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="F48" s="35" t="s">
+        <v>448</v>
+      </c>
+      <c r="G48" s="35" t="s">
+        <v>451</v>
+      </c>
+      <c r="H48" s="35" t="s">
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -3636,16 +3880,16 @@
         <v>61</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1">
@@ -3656,33 +3900,57 @@
         <v>58</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>425</v>
-      </c>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="A18" s="5">
+        <v>43</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="A19" s="5">
+        <v>45</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1">
       <c r="A20" s="5"/>
@@ -3806,7 +4074,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3950,7 +4218,7 @@
         <v>182</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1">
@@ -3978,7 +4246,7 @@
         <v>182</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>387</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1">
@@ -4006,7 +4274,7 @@
         <v>182</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>427</v>
+        <v>465</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6">
@@ -4543,7 +4811,7 @@
         <v>36</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C63" t="s">
         <v>193</v>
@@ -4557,7 +4825,7 @@
         <v>37</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C64" s="33" t="s">
         <v>193</v>
@@ -4571,7 +4839,7 @@
         <v>38</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C65" t="s">
         <v>193</v>
@@ -4585,7 +4853,7 @@
         <v>39</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C66" s="33" t="s">
         <v>193</v>
@@ -4599,12 +4867,82 @@
         <v>40</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C67" s="33" t="s">
         <v>193</v>
       </c>
       <c r="D67" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="43.2">
+      <c r="A68" s="23">
+        <v>41</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C68" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="43.2">
+      <c r="A69" s="23">
+        <v>42</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C69" t="s">
+        <v>193</v>
+      </c>
+      <c r="D69" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="28.8">
+      <c r="A70" s="23">
+        <v>43</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="C70" t="s">
+        <v>193</v>
+      </c>
+      <c r="D70" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="43.2">
+      <c r="A71" s="23">
+        <v>44</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="C71" t="s">
+        <v>193</v>
+      </c>
+      <c r="D71" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="43.2">
+      <c r="A72" s="23">
+        <v>45</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="C72" t="s">
+        <v>193</v>
+      </c>
+      <c r="D72" t="s">
         <v>193</v>
       </c>
     </row>

--- a/AI_AuditLog_Example_HoangNhatKha.xlsx
+++ b/AI_AuditLog_Example_HoangNhatKha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_UNIVERSITY\Kì 5\5.SWP391\swp391-aiauditlog-nhatkhaiphone-ux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083757D9-BCA7-4CBE-B7A4-CB0DEC3F536C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46760337-5F28-49BE-8411-7B0ACF559EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="509">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1428,15 +1428,6 @@
     <t>Re-prompted the AI using precise keywords: "Generate a DROP CONSTRAINT and ADD CONSTRAINT CHECK script for the Status column".</t>
   </si>
   <si>
-    <t>45 entries</t>
-  </si>
-  <si>
-    <t>14 hallucination cases</t>
-  </si>
-  <si>
-    <t>Evidence present for 45/45 entries</t>
-  </si>
-  <si>
     <t>Có – Việc dùng một endpoint thống nhất /api/landlord/rental-requests giúp backend dễ bảo trì route hơn và cho phép frontend xử lý triệt để được lỗi 404.</t>
   </si>
   <si>
@@ -1450,6 +1441,129 @@
   </si>
   <si>
     <t>Có – Sử dụng ràng buộc CHECK Constraint trực tiếp ở tầng database giúp chặn các lỗi sai trạng thái sinh ra từ tầng code, tránh việc làm hỏng dữ liệu.</t>
+  </si>
+  <si>
+    <t>Write a Debounce function for Room Search</t>
+  </si>
+  <si>
+    <t>"When searching for rooms by name, it calls the API on every keystroke. Write a useDebounce custom hook in React to delay the API call."</t>
+  </si>
+  <si>
+    <t>Provided a useDebounce hook using setTimeout and clearTimeout with a 500ms delay.</t>
+  </si>
+  <si>
+    <t>Inserted the hook into the SearchBar, monitored the Network tab, and saw API calls only firing when the user stops typing.</t>
+  </si>
+  <si>
+    <t>Reduced unnecessary API calls by 80%, making the search bar much smoother without lagging.</t>
+  </si>
+  <si>
+    <t>Setup Socket.IO for Real-time Notifications</t>
+  </si>
+  <si>
+    <t>"How do I integrate Socket.IO into the Express backend to send a real-time notification to the landlord when a new rental request is created?"</t>
+  </si>
+  <si>
+    <t>Provided basic io.on('connection') setup and instructions to use io.emit('new_request', data) to send events.</t>
+  </si>
+  <si>
+    <t>Realized that io.emit broadcasts to everyone. Refactored the logic to map userId to socketId for targeted sending.</t>
+  </si>
+  <si>
+    <t>Landlords receive instant notifications for rental requests on their screen without refreshing the page.</t>
+  </si>
+  <si>
+    <t>Write an SQL Pagination query</t>
+  </si>
+  <si>
+    <t>Upload evidence images to Cloudinary</t>
+  </si>
+  <si>
+    <t>Prevent Brute Force Attacks on Login</t>
+  </si>
+  <si>
+    <t>"The room listing API currently returns all data. Give me a standard SQL Server query using OFFSET and FETCH NEXT for pagination."</t>
+  </si>
+  <si>
+    <t>"Users need to send contract images in the chat. Provide setup code for multer and multer-storage-cloudinary to upload an image and get the URL."</t>
+  </si>
+  <si>
+    <t>// Rate limiting middleware to prevent brute force on /login</t>
+  </si>
+  <si>
+    <t>Generated the query ORDER BY Id OFFSET ? ROWS FETCH NEXT ? ROWS ONLY and offset calculation logic.</t>
+  </si>
+  <si>
+    <t>Wrote config middleware upload.single('image') that returns req.file.path.</t>
+  </si>
+  <si>
+    <t>Suggested using express-rate-limit, configured to allow 100 requests per 15 minutes.</t>
+  </si>
+  <si>
+    <t>Tested the query in SSMS, then integrated it into the page and limit API parameters.</t>
+  </si>
+  <si>
+    <t>Tested successfully with Postman but noticed AI forgot size limits. Manually added limits: { fileSize }.</t>
+  </si>
+  <si>
+    <t>100 times is too loose for a Login API. Adjusted the configuration to a stricter 5 requests per 5 minutes.</t>
+  </si>
+  <si>
+    <t>Room listing page loads 3 times faster, correctly displaying 10 rooms per page.</t>
+  </si>
+  <si>
+    <t>The messaging system securely supports image uploads, saving files to Cloudinary.</t>
+  </si>
+  <si>
+    <t>Enhanced system security by preventing hackers from using automated password-guessing tools.</t>
+  </si>
+  <si>
+    <t>Claimed that using io.emit('event_name') is enough to send real-time notifications to the Landlord.</t>
+  </si>
+  <si>
+    <t>Configured Multer file upload setup simply, accepting any file type and size.</t>
+  </si>
+  <si>
+    <t>io.emit is a Broadcast function (sends to all online users). This would cause Landlord A to receive booking notifications meant for Landlord B.</t>
+  </si>
+  <si>
+    <t>Allowing unlimited file sizes and formats could exhaust server memory and allow hackers to upload malicious files (.exe, .sh).</t>
+  </si>
+  <si>
+    <t>Ran a test by opening 2 different Landlord accounts in 2 incognito tabs and saw both receiving the notification.</t>
+  </si>
+  <si>
+    <t>Reviewed the AI-generated middleware code and found no file size limits or MIME type checks.</t>
+  </si>
+  <si>
+    <t>Removed io.emit. Created a userSocketMap to store user IDs. Used io.to(socketId).emit() to send private, targeted notifications.</t>
+  </si>
+  <si>
+    <t>Proactively added limits: { fileSize: 5 * 1024 * 1024 } (max 5MB limit) and a fileFilter function to strictly allow only .jpg and .png extensions.</t>
+  </si>
+  <si>
+    <t>50 entries</t>
+  </si>
+  <si>
+    <t>16 hallucination cases</t>
+  </si>
+  <si>
+    <t>Evidence present for 50/50 entries</t>
+  </si>
+  <si>
+    <t>Có – Hàm Debounce giúp hoãn việc gọi API cho đến khi user ngừng gõ phím. Kỹ thuật này giảm thiểu hàng tá request rác, chống sập database.</t>
+  </si>
+  <si>
+    <t>Có – Việc tạo Map lưu trữ userId -&gt; socketId là bắt buộc. Nếu không có nó, hệ thống không phân biệt được ai là ai để gửi thông báo riêng tư một cách bảo mật.</t>
+  </si>
+  <si>
+    <t>Có – Xử lý phân trang bằng OFFSET / FETCH ở mức Database luôn tối ưu bộ nhớ hơn nhiều so với việc tải cả ngàn dòng dữ liệu lên RAM Server rồi mới cắt mảng (slice).</t>
+  </si>
+  <si>
+    <t>Có – Việc lưu ảnh trên Cloudinary thay vì ổ cứng Local Server giúp server nhẹ hơn, dễ mở rộng (scale) sau này, và tránh bị mất ảnh nếu server sập/deploy lại.</t>
+  </si>
+  <si>
+    <t>Có – Đặt giới hạn truy cập (Rate Limit) chặn đứng các phần mềm tự động dò mật khẩu (dictionary attack), giúp hệ thống đạt chuẩn an toàn bảo mật cơ bản.</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2210,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="15">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2104,7 +2218,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="16">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2112,7 +2226,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="17">
-        <v>0.18</v>
+        <v>0.17860000000000001</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>10</v>
@@ -2123,7 +2237,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="16">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18">
@@ -2236,7 +2350,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>26</v>
@@ -2285,7 +2399,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3571,6 +3685,136 @@
       </c>
       <c r="H48" s="35" t="s">
         <v>454</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="72">
+      <c r="A49" s="34">
+        <v>46</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="D49" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="35" t="s">
+        <v>469</v>
+      </c>
+      <c r="F49" s="35" t="s">
+        <v>470</v>
+      </c>
+      <c r="G49" s="35" t="s">
+        <v>471</v>
+      </c>
+      <c r="H49" s="35" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="72">
+      <c r="A50" s="34">
+        <v>47</v>
+      </c>
+      <c r="B50" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="D50" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F50" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="G50" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="H50" s="35" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="57.6">
+      <c r="A51" s="34">
+        <v>48</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>478</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>484</v>
+      </c>
+      <c r="G51" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="H51" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="72">
+      <c r="A52" s="34">
+        <v>49</v>
+      </c>
+      <c r="B52" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>479</v>
+      </c>
+      <c r="D52" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>482</v>
+      </c>
+      <c r="F52" s="35" t="s">
+        <v>485</v>
+      </c>
+      <c r="G52" s="35" t="s">
+        <v>488</v>
+      </c>
+      <c r="H52" s="35" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="72">
+      <c r="A53" s="34">
+        <v>50</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>480</v>
+      </c>
+      <c r="D53" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>483</v>
+      </c>
+      <c r="F53" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="G53" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="H53" s="35" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -3953,20 +4197,44 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="5">
+        <v>47</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="A21" s="5">
+        <v>49</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="60" customHeight="1">
       <c r="A22" s="5"/>
@@ -4074,7 +4342,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4218,7 +4486,7 @@
         <v>182</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" thickBot="1">
@@ -4246,7 +4514,7 @@
         <v>182</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1">
@@ -4274,7 +4542,7 @@
         <v>182</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>465</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6">
@@ -4881,7 +5149,7 @@
         <v>41</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C68" t="s">
         <v>193</v>
@@ -4895,7 +5163,7 @@
         <v>42</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C69" t="s">
         <v>193</v>
@@ -4909,7 +5177,7 @@
         <v>43</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C70" t="s">
         <v>193</v>
@@ -4923,7 +5191,7 @@
         <v>44</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C71" t="s">
         <v>193</v>
@@ -4937,12 +5205,82 @@
         <v>45</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C72" t="s">
         <v>193</v>
       </c>
       <c r="D72" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="28.8">
+      <c r="A73" s="23">
+        <v>46</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="C73" t="s">
+        <v>193</v>
+      </c>
+      <c r="D73" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="43.2">
+      <c r="A74" s="23">
+        <v>47</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="C74" t="s">
+        <v>193</v>
+      </c>
+      <c r="D74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="43.2">
+      <c r="A75" s="23">
+        <v>48</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C75" t="s">
+        <v>193</v>
+      </c>
+      <c r="D75" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="43.2">
+      <c r="A76" s="23">
+        <v>49</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C76" t="s">
+        <v>193</v>
+      </c>
+      <c r="D76" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="43.2">
+      <c r="A77" s="23">
+        <v>50</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C77" t="s">
+        <v>193</v>
+      </c>
+      <c r="D77" t="s">
         <v>193</v>
       </c>
     </row>
